--- a/NYC_Sales_Dashboard.xlsx
+++ b/NYC_Sales_Dashboard.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="74">
   <si>
     <t>Label</t>
   </si>
@@ -115,6 +115,12 @@
     <t>Total Sales Value (USD)</t>
   </si>
   <si>
+    <t>Gross Sq Ft</t>
+  </si>
+  <si>
+    <t>Sale Price</t>
+  </si>
+  <si>
     <t>NYC Property Sales Dashboard  |  Sep 2016 – Aug 2017</t>
   </si>
   <si>
@@ -154,6 +160,66 @@
     <t>Top Borough (by value)</t>
   </si>
   <si>
+    <t>Q5 — Correlation &amp; Linear Regression: Which Attributes Drive Sale Price?</t>
+  </si>
+  <si>
+    <t>Top predictor: Gross Sq Ft  |  R² = 0.240  |  Equation: Sale Price = 380 x Gross Sq Ft + 15,675  |  p-value = 0.00e+00  |  Sample n = 500</t>
+  </si>
+  <si>
+    <t>Predictor</t>
+  </si>
+  <si>
+    <t>Pearson r</t>
+  </si>
+  <si>
+    <t>Strength</t>
+  </si>
+  <si>
+    <t>Moderate</t>
+  </si>
+  <si>
+    <t>Total Units</t>
+  </si>
+  <si>
+    <t>Res Units</t>
+  </si>
+  <si>
+    <t>Weak</t>
+  </si>
+  <si>
+    <t>Year Built</t>
+  </si>
+  <si>
+    <t>Land Sq Ft</t>
+  </si>
+  <si>
+    <t>Linear Regression Summary</t>
+  </si>
+  <si>
+    <t>Dependent Variable</t>
+  </si>
+  <si>
+    <t>Independent Variable</t>
+  </si>
+  <si>
+    <t>R (correlation)</t>
+  </si>
+  <si>
+    <t>R² (explained var.)</t>
+  </si>
+  <si>
+    <t>Slope (coefficient)</t>
+  </si>
+  <si>
+    <t>Intercept</t>
+  </si>
+  <si>
+    <t>p-value</t>
+  </si>
+  <si>
+    <t>Sample Size</t>
+  </si>
+  <si>
     <t>Q1 Median Sale Price by Borough (All Classes)</t>
   </si>
   <si>
@@ -168,16 +234,23 @@
   <si>
     <t>Q2 Monthly Transactions (All Boroughs)</t>
   </si>
+  <si>
+    <t>Q5 Correlation with Sale Price</t>
+  </si>
+  <si>
+    <t>R squared</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="3">
     <numFmt numFmtId="164" formatCode="#,##0"/>
     <numFmt numFmtId="165" formatCode="$#,##0"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="14">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -256,8 +329,39 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -291,6 +395,42 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF375623"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF548235"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBDD7EE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDEEAF1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -337,7 +477,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -371,6 +511,34 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="0" fillId="9" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="11" fillId="10" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="12" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1146,6 +1314,3179 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <c:lang val="en-US"/>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Q5 — Sale Price vs Gross Sq Ft</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:layout/>
+    </c:title>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Sampled Sales</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="4"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:srgbClr val="4472C4">
+                  <a:alpha val="50000"/>
+                </a:srgbClr>
+              </a:solidFill>
+              <a:ln>
+                <a:solidFill>
+                  <a:srgbClr val="4472C4"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="25400">
+                <a:solidFill>
+                  <a:srgbClr val="FF0000"/>
+                </a:solidFill>
+              </a:ln>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="1"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout/>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>ChartSource!$M$2:$M$501</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="500"/>
+                <c:pt idx="0">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2080</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1165</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>5400</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1820</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1683</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>912</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1248</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2808</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>1312</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>420</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1264</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1518</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1449</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3840</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2065</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>912</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>1152</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>1550</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1050</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1095</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>1750</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>1776</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1526</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>918</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>1172</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1490</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>1152</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>879</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2034</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1936</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1170</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2524</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1706</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>924</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2520</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>1470</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>2590</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1472</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>1440</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>1890</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1440</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>816</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>3280</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1268</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>1380</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1273</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1944</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>1612</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1680</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>884</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>1188</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>1408</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>2002</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2970</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1440</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>2125</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>2010</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>1216</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2280</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1280</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2080</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>1919</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1652</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>1690</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>2280</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>2192</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2280</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>1352</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>906</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>1975</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>1444</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>3600</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>1672</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>1680</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>2160</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>1282</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>1150</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>2254</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>1342</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>1955</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>1118</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>1998</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>1056</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>1232</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>1300</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>1240</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>2108</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>2020</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>3795</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>1551</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>3510</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>1536</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>960</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>2180</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>1490</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>1432</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>1275</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>1472</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>3336</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>3120</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>990</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>2425</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>2604</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>2640</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>872</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>2100</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>1170</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>2360</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>1496</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>4608</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>5244</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>3040</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>2130</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>2280</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>1172</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>3420</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>3280</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>1122</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>2113</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>1224</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>2208</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>1222</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>1764</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>2892</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>1496</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>1354</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>1272</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>1324</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>1568</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>1456</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>3553</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>2078</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>1624</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>2160</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>2120</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>2904</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>1920</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>2350</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>1592</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>1680</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>944</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>2880</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>988</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>3496</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>4852</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>1360</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>1434</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>942</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>1760</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>1512</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>2510</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>3120</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>3348</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>1348</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>1440</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>1136</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>1936</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>1506</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>1256</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>3400</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>1080</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>1760</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>3403</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1536</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>2638</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>1120</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>1833</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>1000</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1565</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>1931</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>1254</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>2156</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>1820</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>3078</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1728</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>2248</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>3256</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>1664</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>1631</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>4435</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>2350</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1408</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>2480</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>1292</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>1008</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>1650</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>2016</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>2391</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>896</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>2952</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>3604</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>1616</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>3720</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>980</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>1008</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>1836</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>1296</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>2250</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>1962</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>1254</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>5400</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>1360</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>2600</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>3700</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>2100</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>1224</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>1320</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>1469</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>1398</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>3150</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>1008</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>5475</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>1813</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>2240</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>1785</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>2052</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>2160</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>1155</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>4400</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>1620</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>3300</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>1620</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>1280</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>1120</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>1272</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>2380</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>1851</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>1936</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>1217</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>1176</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>1332</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>1408</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>2710</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>2597</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>2700</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>2200</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>1600</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>3018</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>3700</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>2940</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>1480</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>1360</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>994</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>2348</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>1234</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>1496</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>2454</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>3453</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>2208</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>1596</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>1200</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>1968</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>1536</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>2250</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>3480</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>3450</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>2044</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>1716</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>1608</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>5280</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>1120</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>2326</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>1556</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>879</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>1640</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>1920</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>1354</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>1234</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>1914</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>1510</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>1120</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>2800</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>1305</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>2943</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>1332</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>3219</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>2360</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>1134</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>2860</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>2220</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>4510</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>1729</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>1440</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>2126</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>2100</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>1242</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>1700</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>1312</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>2244</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>2286</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>1248</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>2048</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>3012</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>2370</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>2600</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>3926</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>1670</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>1584</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>1620</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>1176</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>3082</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>2997</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>1450</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>448</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>1040</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>3521</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>2424</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>3400</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>1824</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>1080</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>2040</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>1696</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>3496</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>1624</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>1653</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>938</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>2523</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>3900</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>3251</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>850</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>2160</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>2246</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>2281</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>1280</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>1744</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>3720</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>1732</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>1120</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>4860</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>1080</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>1125</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>1368</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>2680</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>1224</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>1868</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>1728</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>870</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>2340</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>1710</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>1280</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>3321</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>2268</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>1044</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>1152</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>1040</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>1246</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>625</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>1440</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>1024</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>2490</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>1658</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>2940</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>1848</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>1652</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>2340</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>3890</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>1564</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>1428</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>1152</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>1920</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>3975</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>928</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>3000</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>1288</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>1820</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>1984</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>1144</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>3090</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>2130</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>1492</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>1588</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>1616</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>6630</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>3069</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>1695</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>2440</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>3087</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>1848</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>1776</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>1240</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>1900</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>1278</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>3288</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>1778</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>3768</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>1120</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>5625</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>3060</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>1950</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>1683</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>1680</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>1169</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>2213</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>2880</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>2800</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>2394</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>2400</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>968</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>3180</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>1328</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>3270</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>1364</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>1938</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>3968</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>1880</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>1362</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>2704</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>1534</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>808</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>1548</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>1626</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>2242</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>2178</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>1737</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>938</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>3320</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>1010</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>2220</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>2500</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>2236</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>6000</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>1080</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>1668</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>928</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>2560</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>1304</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>1064</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>1080</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>1620</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>1400</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>1592</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>1598</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>1488</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>3301</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>3265</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>2316</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>1728</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>1386</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>2999</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>1771</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>2280</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>1216</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>952</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>1870</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>1128</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>992</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>1785</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>1012</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>2208</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>1729</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>2100</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>2271</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>4408</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>1944</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>2358</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>1633</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>1552</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>1344</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>1740</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>2622</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>3860</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>1633</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>3360</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>1980</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>1872</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>3078</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>ChartSource!$N$2:$N$501</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="500"/>
+                <c:pt idx="0">
+                  <c:v>1600000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>950000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>640000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>400000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>356420</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>2050000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>570000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>420000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>505000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>920000</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>925000</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>758000</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>110000</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>510000</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>1300000</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>959000</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1150000</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>650000</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>615000</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>500000</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>740000</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>407849</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>720000</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>760000</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>800000</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>635000</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>565000</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>760000</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>360000</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>330000</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>760000</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>485000</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>965000</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>510000</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>630000</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>365000</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>1135000</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>1722800</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>436000</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>625000</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>775000</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>870000</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>590000</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>668000</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>670000</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>750000</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>495000</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>705000</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>390000</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>450000</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>903000</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>650000</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>660000</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1355000</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>329000</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>600000</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>250000</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>579000</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>850000</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>476000</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>550000</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>465000</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>608000</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>975000</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>550000</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>576000</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>698298</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>580000</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>495500</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>486720</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>980000</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>365000</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1230000</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>135000</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>425000</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>760000</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>442000</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>425000</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>927000</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>640000</c:v>
+                </c:pt>
+                <c:pt idx="80">
+                  <c:v>1400000</c:v>
+                </c:pt>
+                <c:pt idx="81">
+                  <c:v>261250</c:v>
+                </c:pt>
+                <c:pt idx="82">
+                  <c:v>685000</c:v>
+                </c:pt>
+                <c:pt idx="83">
+                  <c:v>600000</c:v>
+                </c:pt>
+                <c:pt idx="84">
+                  <c:v>300000</c:v>
+                </c:pt>
+                <c:pt idx="85">
+                  <c:v>720000</c:v>
+                </c:pt>
+                <c:pt idx="86">
+                  <c:v>570000</c:v>
+                </c:pt>
+                <c:pt idx="87">
+                  <c:v>680000</c:v>
+                </c:pt>
+                <c:pt idx="88">
+                  <c:v>640000</c:v>
+                </c:pt>
+                <c:pt idx="89">
+                  <c:v>815000</c:v>
+                </c:pt>
+                <c:pt idx="90">
+                  <c:v>580000</c:v>
+                </c:pt>
+                <c:pt idx="91">
+                  <c:v>540000</c:v>
+                </c:pt>
+                <c:pt idx="92">
+                  <c:v>390000</c:v>
+                </c:pt>
+                <c:pt idx="93">
+                  <c:v>374166</c:v>
+                </c:pt>
+                <c:pt idx="94">
+                  <c:v>520000</c:v>
+                </c:pt>
+                <c:pt idx="95">
+                  <c:v>905000</c:v>
+                </c:pt>
+                <c:pt idx="96">
+                  <c:v>475000</c:v>
+                </c:pt>
+                <c:pt idx="97">
+                  <c:v>710000</c:v>
+                </c:pt>
+                <c:pt idx="98">
+                  <c:v>775000</c:v>
+                </c:pt>
+                <c:pt idx="99">
+                  <c:v>300000</c:v>
+                </c:pt>
+                <c:pt idx="100">
+                  <c:v>475000</c:v>
+                </c:pt>
+                <c:pt idx="101">
+                  <c:v>250000</c:v>
+                </c:pt>
+                <c:pt idx="102">
+                  <c:v>645000</c:v>
+                </c:pt>
+                <c:pt idx="103">
+                  <c:v>350000</c:v>
+                </c:pt>
+                <c:pt idx="104">
+                  <c:v>525000</c:v>
+                </c:pt>
+                <c:pt idx="105">
+                  <c:v>840000</c:v>
+                </c:pt>
+                <c:pt idx="106">
+                  <c:v>920000</c:v>
+                </c:pt>
+                <c:pt idx="107">
+                  <c:v>650000</c:v>
+                </c:pt>
+                <c:pt idx="108">
+                  <c:v>510000</c:v>
+                </c:pt>
+                <c:pt idx="109">
+                  <c:v>999000</c:v>
+                </c:pt>
+                <c:pt idx="110">
+                  <c:v>1760000</c:v>
+                </c:pt>
+                <c:pt idx="111">
+                  <c:v>450000</c:v>
+                </c:pt>
+                <c:pt idx="112">
+                  <c:v>880000</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>381250</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>275000</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>515000</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>460000</c:v>
+                </c:pt>
+                <c:pt idx="117">
+                  <c:v>510000</c:v>
+                </c:pt>
+                <c:pt idx="118">
+                  <c:v>795000</c:v>
+                </c:pt>
+                <c:pt idx="119">
+                  <c:v>1440000</c:v>
+                </c:pt>
+                <c:pt idx="120">
+                  <c:v>750000</c:v>
+                </c:pt>
+                <c:pt idx="121">
+                  <c:v>9900000</c:v>
+                </c:pt>
+                <c:pt idx="122">
+                  <c:v>3150000</c:v>
+                </c:pt>
+                <c:pt idx="123">
+                  <c:v>165000</c:v>
+                </c:pt>
+                <c:pt idx="124">
+                  <c:v>470000</c:v>
+                </c:pt>
+                <c:pt idx="125">
+                  <c:v>430000</c:v>
+                </c:pt>
+                <c:pt idx="126">
+                  <c:v>550000</c:v>
+                </c:pt>
+                <c:pt idx="127">
+                  <c:v>1250000</c:v>
+                </c:pt>
+                <c:pt idx="128">
+                  <c:v>786500</c:v>
+                </c:pt>
+                <c:pt idx="129">
+                  <c:v>768000</c:v>
+                </c:pt>
+                <c:pt idx="130">
+                  <c:v>880000</c:v>
+                </c:pt>
+                <c:pt idx="131">
+                  <c:v>1090000</c:v>
+                </c:pt>
+                <c:pt idx="132">
+                  <c:v>180000</c:v>
+                </c:pt>
+                <c:pt idx="133">
+                  <c:v>350000</c:v>
+                </c:pt>
+                <c:pt idx="134">
+                  <c:v>515000</c:v>
+                </c:pt>
+                <c:pt idx="135">
+                  <c:v>545000</c:v>
+                </c:pt>
+                <c:pt idx="136">
+                  <c:v>1180000</c:v>
+                </c:pt>
+                <c:pt idx="137">
+                  <c:v>728000</c:v>
+                </c:pt>
+                <c:pt idx="138">
+                  <c:v>295000</c:v>
+                </c:pt>
+                <c:pt idx="139">
+                  <c:v>410000</c:v>
+                </c:pt>
+                <c:pt idx="140">
+                  <c:v>715000</c:v>
+                </c:pt>
+                <c:pt idx="141">
+                  <c:v>589000</c:v>
+                </c:pt>
+                <c:pt idx="142">
+                  <c:v>915000</c:v>
+                </c:pt>
+                <c:pt idx="143">
+                  <c:v>1362000</c:v>
+                </c:pt>
+                <c:pt idx="144">
+                  <c:v>643400</c:v>
+                </c:pt>
+                <c:pt idx="145">
+                  <c:v>265000</c:v>
+                </c:pt>
+                <c:pt idx="146">
+                  <c:v>995000</c:v>
+                </c:pt>
+                <c:pt idx="147">
+                  <c:v>895000</c:v>
+                </c:pt>
+                <c:pt idx="148">
+                  <c:v>595000</c:v>
+                </c:pt>
+                <c:pt idx="149">
+                  <c:v>890000</c:v>
+                </c:pt>
+                <c:pt idx="150">
+                  <c:v>1430000</c:v>
+                </c:pt>
+                <c:pt idx="151">
+                  <c:v>560000</c:v>
+                </c:pt>
+                <c:pt idx="152">
+                  <c:v>689000</c:v>
+                </c:pt>
+                <c:pt idx="153">
+                  <c:v>573000</c:v>
+                </c:pt>
+                <c:pt idx="154">
+                  <c:v>450000</c:v>
+                </c:pt>
+                <c:pt idx="155">
+                  <c:v>405000</c:v>
+                </c:pt>
+                <c:pt idx="156">
+                  <c:v>4600000</c:v>
+                </c:pt>
+                <c:pt idx="157">
+                  <c:v>429000</c:v>
+                </c:pt>
+                <c:pt idx="158">
+                  <c:v>5650000</c:v>
+                </c:pt>
+                <c:pt idx="159">
+                  <c:v>3300000</c:v>
+                </c:pt>
+                <c:pt idx="160">
+                  <c:v>525000</c:v>
+                </c:pt>
+                <c:pt idx="161">
+                  <c:v>650000</c:v>
+                </c:pt>
+                <c:pt idx="162">
+                  <c:v>890968</c:v>
+                </c:pt>
+                <c:pt idx="163">
+                  <c:v>562000</c:v>
+                </c:pt>
+                <c:pt idx="164">
+                  <c:v>42500</c:v>
+                </c:pt>
+                <c:pt idx="165">
+                  <c:v>730000</c:v>
+                </c:pt>
+                <c:pt idx="166">
+                  <c:v>1150000</c:v>
+                </c:pt>
+                <c:pt idx="167">
+                  <c:v>528000</c:v>
+                </c:pt>
+                <c:pt idx="168">
+                  <c:v>266600</c:v>
+                </c:pt>
+                <c:pt idx="169">
+                  <c:v>316863</c:v>
+                </c:pt>
+                <c:pt idx="170">
+                  <c:v>389000</c:v>
+                </c:pt>
+                <c:pt idx="171">
+                  <c:v>498000</c:v>
+                </c:pt>
+                <c:pt idx="172">
+                  <c:v>675000</c:v>
+                </c:pt>
+                <c:pt idx="173">
+                  <c:v>540000</c:v>
+                </c:pt>
+                <c:pt idx="174">
+                  <c:v>668000</c:v>
+                </c:pt>
+                <c:pt idx="175">
+                  <c:v>999000</c:v>
+                </c:pt>
+                <c:pt idx="176">
+                  <c:v>710000</c:v>
+                </c:pt>
+                <c:pt idx="177">
+                  <c:v>600000</c:v>
+                </c:pt>
+                <c:pt idx="178">
+                  <c:v>525000</c:v>
+                </c:pt>
+                <c:pt idx="179">
+                  <c:v>1080000</c:v>
+                </c:pt>
+                <c:pt idx="180">
+                  <c:v>1575000</c:v>
+                </c:pt>
+                <c:pt idx="181">
+                  <c:v>310000</c:v>
+                </c:pt>
+                <c:pt idx="182">
+                  <c:v>570000</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>291000</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>1325000</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>660000</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>350000</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>515000</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>327500</c:v>
+                </c:pt>
+                <c:pt idx="189">
+                  <c:v>675000</c:v>
+                </c:pt>
+                <c:pt idx="190">
+                  <c:v>1753110</c:v>
+                </c:pt>
+                <c:pt idx="191">
+                  <c:v>286000</c:v>
+                </c:pt>
+                <c:pt idx="192">
+                  <c:v>1633333</c:v>
+                </c:pt>
+                <c:pt idx="193">
+                  <c:v>250000</c:v>
+                </c:pt>
+                <c:pt idx="194">
+                  <c:v>150000</c:v>
+                </c:pt>
+                <c:pt idx="195">
+                  <c:v>850000</c:v>
+                </c:pt>
+                <c:pt idx="196">
+                  <c:v>680000</c:v>
+                </c:pt>
+                <c:pt idx="197">
+                  <c:v>1050000</c:v>
+                </c:pt>
+                <c:pt idx="198">
+                  <c:v>1360000</c:v>
+                </c:pt>
+                <c:pt idx="199">
+                  <c:v>800000</c:v>
+                </c:pt>
+                <c:pt idx="200">
+                  <c:v>225000</c:v>
+                </c:pt>
+                <c:pt idx="201">
+                  <c:v>435000</c:v>
+                </c:pt>
+                <c:pt idx="202">
+                  <c:v>310000</c:v>
+                </c:pt>
+                <c:pt idx="203">
+                  <c:v>2000000</c:v>
+                </c:pt>
+                <c:pt idx="204">
+                  <c:v>790000</c:v>
+                </c:pt>
+                <c:pt idx="205">
+                  <c:v>670000</c:v>
+                </c:pt>
+                <c:pt idx="206">
+                  <c:v>415000</c:v>
+                </c:pt>
+                <c:pt idx="207">
+                  <c:v>323534</c:v>
+                </c:pt>
+                <c:pt idx="208">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="209">
+                  <c:v>1500000</c:v>
+                </c:pt>
+                <c:pt idx="210">
+                  <c:v>305000</c:v>
+                </c:pt>
+                <c:pt idx="211">
+                  <c:v>800000</c:v>
+                </c:pt>
+                <c:pt idx="212">
+                  <c:v>100000</c:v>
+                </c:pt>
+                <c:pt idx="213">
+                  <c:v>390000</c:v>
+                </c:pt>
+                <c:pt idx="214">
+                  <c:v>845000</c:v>
+                </c:pt>
+                <c:pt idx="215">
+                  <c:v>790000</c:v>
+                </c:pt>
+                <c:pt idx="216">
+                  <c:v>790000</c:v>
+                </c:pt>
+                <c:pt idx="217">
+                  <c:v>497800</c:v>
+                </c:pt>
+                <c:pt idx="218">
+                  <c:v>700000</c:v>
+                </c:pt>
+                <c:pt idx="219">
+                  <c:v>600000</c:v>
+                </c:pt>
+                <c:pt idx="220">
+                  <c:v>572000</c:v>
+                </c:pt>
+                <c:pt idx="221">
+                  <c:v>7090000</c:v>
+                </c:pt>
+                <c:pt idx="222">
+                  <c:v>1230000</c:v>
+                </c:pt>
+                <c:pt idx="223">
+                  <c:v>1270000</c:v>
+                </c:pt>
+                <c:pt idx="224">
+                  <c:v>539000</c:v>
+                </c:pt>
+                <c:pt idx="225">
+                  <c:v>400000</c:v>
+                </c:pt>
+                <c:pt idx="226">
+                  <c:v>379000</c:v>
+                </c:pt>
+                <c:pt idx="227">
+                  <c:v>610000</c:v>
+                </c:pt>
+                <c:pt idx="228">
+                  <c:v>335000</c:v>
+                </c:pt>
+                <c:pt idx="229">
+                  <c:v>820000</c:v>
+                </c:pt>
+                <c:pt idx="230">
+                  <c:v>1421175</c:v>
+                </c:pt>
+                <c:pt idx="231">
+                  <c:v>590000</c:v>
+                </c:pt>
+                <c:pt idx="232">
+                  <c:v>228500</c:v>
+                </c:pt>
+                <c:pt idx="233">
+                  <c:v>720000</c:v>
+                </c:pt>
+                <c:pt idx="234">
+                  <c:v>500000</c:v>
+                </c:pt>
+                <c:pt idx="235">
+                  <c:v>1300000</c:v>
+                </c:pt>
+                <c:pt idx="236">
+                  <c:v>655000</c:v>
+                </c:pt>
+                <c:pt idx="237">
+                  <c:v>479838</c:v>
+                </c:pt>
+                <c:pt idx="238">
+                  <c:v>1472074</c:v>
+                </c:pt>
+                <c:pt idx="239">
+                  <c:v>998500</c:v>
+                </c:pt>
+                <c:pt idx="240">
+                  <c:v>385000</c:v>
+                </c:pt>
+                <c:pt idx="241">
+                  <c:v>420000</c:v>
+                </c:pt>
+                <c:pt idx="242">
+                  <c:v>441090</c:v>
+                </c:pt>
+                <c:pt idx="243">
+                  <c:v>485000</c:v>
+                </c:pt>
+                <c:pt idx="244">
+                  <c:v>892000</c:v>
+                </c:pt>
+                <c:pt idx="245">
+                  <c:v>230000</c:v>
+                </c:pt>
+                <c:pt idx="246">
+                  <c:v>710000</c:v>
+                </c:pt>
+                <c:pt idx="247">
+                  <c:v>935000</c:v>
+                </c:pt>
+                <c:pt idx="248">
+                  <c:v>855000</c:v>
+                </c:pt>
+                <c:pt idx="249">
+                  <c:v>95000</c:v>
+                </c:pt>
+                <c:pt idx="250">
+                  <c:v>445000</c:v>
+                </c:pt>
+                <c:pt idx="251">
+                  <c:v>600000</c:v>
+                </c:pt>
+                <c:pt idx="252">
+                  <c:v>450000</c:v>
+                </c:pt>
+                <c:pt idx="253">
+                  <c:v>162500</c:v>
+                </c:pt>
+                <c:pt idx="254">
+                  <c:v>1388888</c:v>
+                </c:pt>
+                <c:pt idx="255">
+                  <c:v>560000</c:v>
+                </c:pt>
+                <c:pt idx="256">
+                  <c:v>457000</c:v>
+                </c:pt>
+                <c:pt idx="257">
+                  <c:v>700000</c:v>
+                </c:pt>
+                <c:pt idx="258">
+                  <c:v>400000</c:v>
+                </c:pt>
+                <c:pt idx="259">
+                  <c:v>551500</c:v>
+                </c:pt>
+                <c:pt idx="260">
+                  <c:v>570000</c:v>
+                </c:pt>
+                <c:pt idx="261">
+                  <c:v>600000</c:v>
+                </c:pt>
+                <c:pt idx="262">
+                  <c:v>665000</c:v>
+                </c:pt>
+                <c:pt idx="263">
+                  <c:v>1325000</c:v>
+                </c:pt>
+                <c:pt idx="264">
+                  <c:v>350000</c:v>
+                </c:pt>
+                <c:pt idx="265">
+                  <c:v>294000</c:v>
+                </c:pt>
+                <c:pt idx="266">
+                  <c:v>950000</c:v>
+                </c:pt>
+                <c:pt idx="267">
+                  <c:v>390000</c:v>
+                </c:pt>
+                <c:pt idx="268">
+                  <c:v>3050000</c:v>
+                </c:pt>
+                <c:pt idx="269">
+                  <c:v>730000</c:v>
+                </c:pt>
+                <c:pt idx="270">
+                  <c:v>230500</c:v>
+                </c:pt>
+                <c:pt idx="271">
+                  <c:v>1750000</c:v>
+                </c:pt>
+                <c:pt idx="272">
+                  <c:v>375000</c:v>
+                </c:pt>
+                <c:pt idx="273">
+                  <c:v>404586</c:v>
+                </c:pt>
+                <c:pt idx="274">
+                  <c:v>868000</c:v>
+                </c:pt>
+                <c:pt idx="275">
+                  <c:v>485000</c:v>
+                </c:pt>
+                <c:pt idx="276">
+                  <c:v>420000</c:v>
+                </c:pt>
+                <c:pt idx="277">
+                  <c:v>1200000</c:v>
+                </c:pt>
+                <c:pt idx="278">
+                  <c:v>160000</c:v>
+                </c:pt>
+                <c:pt idx="279">
+                  <c:v>1150000</c:v>
+                </c:pt>
+                <c:pt idx="280">
+                  <c:v>1300000</c:v>
+                </c:pt>
+                <c:pt idx="281">
+                  <c:v>345000</c:v>
+                </c:pt>
+                <c:pt idx="282">
+                  <c:v>370000</c:v>
+                </c:pt>
+                <c:pt idx="283">
+                  <c:v>840520</c:v>
+                </c:pt>
+                <c:pt idx="284">
+                  <c:v>238780</c:v>
+                </c:pt>
+                <c:pt idx="285">
+                  <c:v>498200</c:v>
+                </c:pt>
+                <c:pt idx="286">
+                  <c:v>645000</c:v>
+                </c:pt>
+                <c:pt idx="287">
+                  <c:v>638000</c:v>
+                </c:pt>
+                <c:pt idx="288">
+                  <c:v>600000</c:v>
+                </c:pt>
+                <c:pt idx="289">
+                  <c:v>510000</c:v>
+                </c:pt>
+                <c:pt idx="290">
+                  <c:v>630000</c:v>
+                </c:pt>
+                <c:pt idx="291">
+                  <c:v>337500</c:v>
+                </c:pt>
+                <c:pt idx="292">
+                  <c:v>345560</c:v>
+                </c:pt>
+                <c:pt idx="293">
+                  <c:v>610000</c:v>
+                </c:pt>
+                <c:pt idx="294">
+                  <c:v>535000</c:v>
+                </c:pt>
+                <c:pt idx="295">
+                  <c:v>740000</c:v>
+                </c:pt>
+                <c:pt idx="296">
+                  <c:v>451230</c:v>
+                </c:pt>
+                <c:pt idx="297">
+                  <c:v>643500</c:v>
+                </c:pt>
+                <c:pt idx="298">
+                  <c:v>700000</c:v>
+                </c:pt>
+                <c:pt idx="299">
+                  <c:v>3000000</c:v>
+                </c:pt>
+                <c:pt idx="300">
+                  <c:v>55394</c:v>
+                </c:pt>
+                <c:pt idx="301">
+                  <c:v>715000</c:v>
+                </c:pt>
+                <c:pt idx="302">
+                  <c:v>640000</c:v>
+                </c:pt>
+                <c:pt idx="303">
+                  <c:v>435000</c:v>
+                </c:pt>
+                <c:pt idx="304">
+                  <c:v>530000</c:v>
+                </c:pt>
+                <c:pt idx="305">
+                  <c:v>1650000</c:v>
+                </c:pt>
+                <c:pt idx="306">
+                  <c:v>600000</c:v>
+                </c:pt>
+                <c:pt idx="307">
+                  <c:v>350000</c:v>
+                </c:pt>
+                <c:pt idx="308">
+                  <c:v>350000</c:v>
+                </c:pt>
+                <c:pt idx="309">
+                  <c:v>860000</c:v>
+                </c:pt>
+                <c:pt idx="310">
+                  <c:v>350000</c:v>
+                </c:pt>
+                <c:pt idx="311">
+                  <c:v>468000</c:v>
+                </c:pt>
+                <c:pt idx="312">
+                  <c:v>530000</c:v>
+                </c:pt>
+                <c:pt idx="313">
+                  <c:v>673000</c:v>
+                </c:pt>
+                <c:pt idx="314">
+                  <c:v>740000</c:v>
+                </c:pt>
+                <c:pt idx="315">
+                  <c:v>753403</c:v>
+                </c:pt>
+                <c:pt idx="316">
+                  <c:v>480000</c:v>
+                </c:pt>
+                <c:pt idx="317">
+                  <c:v>560000</c:v>
+                </c:pt>
+                <c:pt idx="318">
+                  <c:v>1320000</c:v>
+                </c:pt>
+                <c:pt idx="319">
+                  <c:v>1555677</c:v>
+                </c:pt>
+                <c:pt idx="320">
+                  <c:v>499000</c:v>
+                </c:pt>
+                <c:pt idx="321">
+                  <c:v>1450000</c:v>
+                </c:pt>
+                <c:pt idx="322">
+                  <c:v>840000</c:v>
+                </c:pt>
+                <c:pt idx="323">
+                  <c:v>655000</c:v>
+                </c:pt>
+                <c:pt idx="324">
+                  <c:v>783484</c:v>
+                </c:pt>
+                <c:pt idx="325">
+                  <c:v>480000</c:v>
+                </c:pt>
+                <c:pt idx="326">
+                  <c:v>1950000</c:v>
+                </c:pt>
+                <c:pt idx="327">
+                  <c:v>1120000</c:v>
+                </c:pt>
+                <c:pt idx="328">
+                  <c:v>580000</c:v>
+                </c:pt>
+                <c:pt idx="329">
+                  <c:v>285500</c:v>
+                </c:pt>
+                <c:pt idx="330">
+                  <c:v>675000</c:v>
+                </c:pt>
+                <c:pt idx="331">
+                  <c:v>200000</c:v>
+                </c:pt>
+                <c:pt idx="332">
+                  <c:v>1110000</c:v>
+                </c:pt>
+                <c:pt idx="333">
+                  <c:v>1020000</c:v>
+                </c:pt>
+                <c:pt idx="334">
+                  <c:v>5510000</c:v>
+                </c:pt>
+                <c:pt idx="335">
+                  <c:v>3045000</c:v>
+                </c:pt>
+                <c:pt idx="336">
+                  <c:v>698000</c:v>
+                </c:pt>
+                <c:pt idx="337">
+                  <c:v>1300000</c:v>
+                </c:pt>
+                <c:pt idx="338">
+                  <c:v>920000</c:v>
+                </c:pt>
+                <c:pt idx="339">
+                  <c:v>1400000</c:v>
+                </c:pt>
+                <c:pt idx="340">
+                  <c:v>290000</c:v>
+                </c:pt>
+                <c:pt idx="341">
+                  <c:v>992000</c:v>
+                </c:pt>
+                <c:pt idx="342">
+                  <c:v>620000</c:v>
+                </c:pt>
+                <c:pt idx="343">
+                  <c:v>1648000</c:v>
+                </c:pt>
+                <c:pt idx="344">
+                  <c:v>2000000</c:v>
+                </c:pt>
+                <c:pt idx="345">
+                  <c:v>533000</c:v>
+                </c:pt>
+                <c:pt idx="346">
+                  <c:v>499999</c:v>
+                </c:pt>
+                <c:pt idx="347">
+                  <c:v>835000</c:v>
+                </c:pt>
+                <c:pt idx="348">
+                  <c:v>715000</c:v>
+                </c:pt>
+                <c:pt idx="349">
+                  <c:v>470000</c:v>
+                </c:pt>
+                <c:pt idx="350">
+                  <c:v>396500</c:v>
+                </c:pt>
+                <c:pt idx="351">
+                  <c:v>729000</c:v>
+                </c:pt>
+                <c:pt idx="352">
+                  <c:v>1400000</c:v>
+                </c:pt>
+                <c:pt idx="353">
+                  <c:v>728000</c:v>
+                </c:pt>
+                <c:pt idx="354">
+                  <c:v>352000</c:v>
+                </c:pt>
+                <c:pt idx="355">
+                  <c:v>1200000</c:v>
+                </c:pt>
+                <c:pt idx="356">
+                  <c:v>690000</c:v>
+                </c:pt>
+                <c:pt idx="357">
+                  <c:v>625000</c:v>
+                </c:pt>
+                <c:pt idx="358">
+                  <c:v>325000</c:v>
+                </c:pt>
+                <c:pt idx="359">
+                  <c:v>630000</c:v>
+                </c:pt>
+                <c:pt idx="360">
+                  <c:v>740000</c:v>
+                </c:pt>
+                <c:pt idx="361">
+                  <c:v>385000</c:v>
+                </c:pt>
+                <c:pt idx="362">
+                  <c:v>380000</c:v>
+                </c:pt>
+                <c:pt idx="363">
+                  <c:v>784000</c:v>
+                </c:pt>
+                <c:pt idx="364">
+                  <c:v>700000</c:v>
+                </c:pt>
+                <c:pt idx="365">
+                  <c:v>1275000</c:v>
+                </c:pt>
+                <c:pt idx="366">
+                  <c:v>469000</c:v>
+                </c:pt>
+                <c:pt idx="367">
+                  <c:v>1300000</c:v>
+                </c:pt>
+                <c:pt idx="368">
+                  <c:v>650000</c:v>
+                </c:pt>
+                <c:pt idx="369">
+                  <c:v>690000</c:v>
+                </c:pt>
+                <c:pt idx="370">
+                  <c:v>330000</c:v>
+                </c:pt>
+                <c:pt idx="371">
+                  <c:v>260000</c:v>
+                </c:pt>
+                <c:pt idx="372">
+                  <c:v>420000</c:v>
+                </c:pt>
+                <c:pt idx="373">
+                  <c:v>300000</c:v>
+                </c:pt>
+                <c:pt idx="374">
+                  <c:v>245000</c:v>
+                </c:pt>
+                <c:pt idx="375">
+                  <c:v>541000</c:v>
+                </c:pt>
+                <c:pt idx="376">
+                  <c:v>510000</c:v>
+                </c:pt>
+                <c:pt idx="377">
+                  <c:v>106000</c:v>
+                </c:pt>
+                <c:pt idx="378">
+                  <c:v>680000</c:v>
+                </c:pt>
+                <c:pt idx="379">
+                  <c:v>390000</c:v>
+                </c:pt>
+                <c:pt idx="380">
+                  <c:v>2125000</c:v>
+                </c:pt>
+                <c:pt idx="381">
+                  <c:v>11750</c:v>
+                </c:pt>
+                <c:pt idx="382">
+                  <c:v>700000</c:v>
+                </c:pt>
+                <c:pt idx="383">
+                  <c:v>535000</c:v>
+                </c:pt>
+                <c:pt idx="384">
+                  <c:v>2700000</c:v>
+                </c:pt>
+                <c:pt idx="385">
+                  <c:v>333500</c:v>
+                </c:pt>
+                <c:pt idx="386">
+                  <c:v>565000</c:v>
+                </c:pt>
+                <c:pt idx="387">
+                  <c:v>370000</c:v>
+                </c:pt>
+                <c:pt idx="388">
+                  <c:v>870000</c:v>
+                </c:pt>
+                <c:pt idx="389">
+                  <c:v>450000</c:v>
+                </c:pt>
+                <c:pt idx="390">
+                  <c:v>700000</c:v>
+                </c:pt>
+                <c:pt idx="391">
+                  <c:v>1210000</c:v>
+                </c:pt>
+                <c:pt idx="392">
+                  <c:v>860000</c:v>
+                </c:pt>
+                <c:pt idx="393">
+                  <c:v>460000</c:v>
+                </c:pt>
+                <c:pt idx="394">
+                  <c:v>659000</c:v>
+                </c:pt>
+                <c:pt idx="395">
+                  <c:v>494000</c:v>
+                </c:pt>
+                <c:pt idx="396">
+                  <c:v>350000</c:v>
+                </c:pt>
+                <c:pt idx="397">
+                  <c:v>1600000</c:v>
+                </c:pt>
+                <c:pt idx="398">
+                  <c:v>550000</c:v>
+                </c:pt>
+                <c:pt idx="399">
+                  <c:v>393000</c:v>
+                </c:pt>
+                <c:pt idx="400">
+                  <c:v>660000</c:v>
+                </c:pt>
+                <c:pt idx="401">
+                  <c:v>430000</c:v>
+                </c:pt>
+                <c:pt idx="402">
+                  <c:v>5200000</c:v>
+                </c:pt>
+                <c:pt idx="403">
+                  <c:v>1330000</c:v>
+                </c:pt>
+                <c:pt idx="404">
+                  <c:v>970000</c:v>
+                </c:pt>
+                <c:pt idx="405">
+                  <c:v>935000</c:v>
+                </c:pt>
+                <c:pt idx="406">
+                  <c:v>466440</c:v>
+                </c:pt>
+                <c:pt idx="407">
+                  <c:v>425000</c:v>
+                </c:pt>
+                <c:pt idx="408">
+                  <c:v>750000</c:v>
+                </c:pt>
+                <c:pt idx="409">
+                  <c:v>660000</c:v>
+                </c:pt>
+                <c:pt idx="410">
+                  <c:v>390000</c:v>
+                </c:pt>
+                <c:pt idx="411">
+                  <c:v>748000</c:v>
+                </c:pt>
+                <c:pt idx="412">
+                  <c:v>505000</c:v>
+                </c:pt>
+                <c:pt idx="413">
+                  <c:v>882500</c:v>
+                </c:pt>
+                <c:pt idx="414">
+                  <c:v>328730</c:v>
+                </c:pt>
+                <c:pt idx="415">
+                  <c:v>2232500</c:v>
+                </c:pt>
+                <c:pt idx="416">
+                  <c:v>670000</c:v>
+                </c:pt>
+                <c:pt idx="417">
+                  <c:v>197500</c:v>
+                </c:pt>
+                <c:pt idx="418">
+                  <c:v>561000</c:v>
+                </c:pt>
+                <c:pt idx="419">
+                  <c:v>659000</c:v>
+                </c:pt>
+                <c:pt idx="420">
+                  <c:v>550000</c:v>
+                </c:pt>
+                <c:pt idx="421">
+                  <c:v>830000</c:v>
+                </c:pt>
+                <c:pt idx="422">
+                  <c:v>430000</c:v>
+                </c:pt>
+                <c:pt idx="423">
+                  <c:v>975000</c:v>
+                </c:pt>
+                <c:pt idx="424">
+                  <c:v>2950000</c:v>
+                </c:pt>
+                <c:pt idx="425">
+                  <c:v>1180000</c:v>
+                </c:pt>
+                <c:pt idx="426">
+                  <c:v>530000</c:v>
+                </c:pt>
+                <c:pt idx="427">
+                  <c:v>1175000</c:v>
+                </c:pt>
+                <c:pt idx="428">
+                  <c:v>700000</c:v>
+                </c:pt>
+                <c:pt idx="429">
+                  <c:v>600000</c:v>
+                </c:pt>
+                <c:pt idx="430">
+                  <c:v>984000</c:v>
+                </c:pt>
+                <c:pt idx="431">
+                  <c:v>300000</c:v>
+                </c:pt>
+                <c:pt idx="432">
+                  <c:v>995000</c:v>
+                </c:pt>
+                <c:pt idx="433">
+                  <c:v>750000</c:v>
+                </c:pt>
+                <c:pt idx="434">
+                  <c:v>580000</c:v>
+                </c:pt>
+                <c:pt idx="435">
+                  <c:v>150000</c:v>
+                </c:pt>
+                <c:pt idx="436">
+                  <c:v>591700</c:v>
+                </c:pt>
+                <c:pt idx="437">
+                  <c:v>418000</c:v>
+                </c:pt>
+                <c:pt idx="438">
+                  <c:v>700000</c:v>
+                </c:pt>
+                <c:pt idx="439">
+                  <c:v>685000</c:v>
+                </c:pt>
+                <c:pt idx="440">
+                  <c:v>410000</c:v>
+                </c:pt>
+                <c:pt idx="441">
+                  <c:v>655000</c:v>
+                </c:pt>
+                <c:pt idx="442">
+                  <c:v>335000</c:v>
+                </c:pt>
+                <c:pt idx="443">
+                  <c:v>430000</c:v>
+                </c:pt>
+                <c:pt idx="444">
+                  <c:v>860000</c:v>
+                </c:pt>
+                <c:pt idx="445">
+                  <c:v>630000</c:v>
+                </c:pt>
+                <c:pt idx="446">
+                  <c:v>1200000</c:v>
+                </c:pt>
+                <c:pt idx="447">
+                  <c:v>455000</c:v>
+                </c:pt>
+                <c:pt idx="448">
+                  <c:v>430000</c:v>
+                </c:pt>
+                <c:pt idx="449">
+                  <c:v>260000</c:v>
+                </c:pt>
+                <c:pt idx="450">
+                  <c:v>319000</c:v>
+                </c:pt>
+                <c:pt idx="451">
+                  <c:v>505000</c:v>
+                </c:pt>
+                <c:pt idx="452">
+                  <c:v>1250000</c:v>
+                </c:pt>
+                <c:pt idx="453">
+                  <c:v>1048000</c:v>
+                </c:pt>
+                <c:pt idx="454">
+                  <c:v>2720000</c:v>
+                </c:pt>
+                <c:pt idx="455">
+                  <c:v>628000</c:v>
+                </c:pt>
+                <c:pt idx="456">
+                  <c:v>475000</c:v>
+                </c:pt>
+                <c:pt idx="457">
+                  <c:v>295000</c:v>
+                </c:pt>
+                <c:pt idx="458">
+                  <c:v>825000</c:v>
+                </c:pt>
+                <c:pt idx="459">
+                  <c:v>450000</c:v>
+                </c:pt>
+                <c:pt idx="460">
+                  <c:v>420000</c:v>
+                </c:pt>
+                <c:pt idx="461">
+                  <c:v>385000</c:v>
+                </c:pt>
+                <c:pt idx="462">
+                  <c:v>299250</c:v>
+                </c:pt>
+                <c:pt idx="463">
+                  <c:v>1550000</c:v>
+                </c:pt>
+                <c:pt idx="464">
+                  <c:v>500000</c:v>
+                </c:pt>
+                <c:pt idx="465">
+                  <c:v>475000</c:v>
+                </c:pt>
+                <c:pt idx="466">
+                  <c:v>382203</c:v>
+                </c:pt>
+                <c:pt idx="467">
+                  <c:v>735000</c:v>
+                </c:pt>
+                <c:pt idx="468">
+                  <c:v>1250000</c:v>
+                </c:pt>
+                <c:pt idx="469">
+                  <c:v>928500</c:v>
+                </c:pt>
+                <c:pt idx="470">
+                  <c:v>540000</c:v>
+                </c:pt>
+                <c:pt idx="471">
+                  <c:v>524000</c:v>
+                </c:pt>
+                <c:pt idx="472">
+                  <c:v>1230000</c:v>
+                </c:pt>
+                <c:pt idx="473">
+                  <c:v>650000</c:v>
+                </c:pt>
+                <c:pt idx="474">
+                  <c:v>1250000</c:v>
+                </c:pt>
+                <c:pt idx="475">
+                  <c:v>505000</c:v>
+                </c:pt>
+                <c:pt idx="476">
+                  <c:v>465000</c:v>
+                </c:pt>
+                <c:pt idx="477">
+                  <c:v>630000</c:v>
+                </c:pt>
+                <c:pt idx="478">
+                  <c:v>640000</c:v>
+                </c:pt>
+                <c:pt idx="479">
+                  <c:v>786000</c:v>
+                </c:pt>
+                <c:pt idx="480">
+                  <c:v>520000</c:v>
+                </c:pt>
+                <c:pt idx="481">
+                  <c:v>450000</c:v>
+                </c:pt>
+                <c:pt idx="482">
+                  <c:v>830000</c:v>
+                </c:pt>
+                <c:pt idx="483">
+                  <c:v>545000</c:v>
+                </c:pt>
+                <c:pt idx="484">
+                  <c:v>600000</c:v>
+                </c:pt>
+                <c:pt idx="485">
+                  <c:v>1100000</c:v>
+                </c:pt>
+                <c:pt idx="486">
+                  <c:v>1780000</c:v>
+                </c:pt>
+                <c:pt idx="487">
+                  <c:v>425000</c:v>
+                </c:pt>
+                <c:pt idx="488">
+                  <c:v>860000</c:v>
+                </c:pt>
+                <c:pt idx="489">
+                  <c:v>738000</c:v>
+                </c:pt>
+                <c:pt idx="490">
+                  <c:v>150000</c:v>
+                </c:pt>
+                <c:pt idx="491">
+                  <c:v>341250</c:v>
+                </c:pt>
+                <c:pt idx="492">
+                  <c:v>420000</c:v>
+                </c:pt>
+                <c:pt idx="493">
+                  <c:v>1400000</c:v>
+                </c:pt>
+                <c:pt idx="494">
+                  <c:v>2850000</c:v>
+                </c:pt>
+                <c:pt idx="495">
+                  <c:v>355000</c:v>
+                </c:pt>
+                <c:pt idx="496">
+                  <c:v>1651000</c:v>
+                </c:pt>
+                <c:pt idx="497">
+                  <c:v>280000</c:v>
+                </c:pt>
+                <c:pt idx="498">
+                  <c:v>800000</c:v>
+                </c:pt>
+                <c:pt idx="499">
+                  <c:v>974000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+        </c:ser>
+        <c:axId val="50050001"/>
+        <c:axId val="50050002"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="50050001"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="b"/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Gross Sq Ft</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="#,##0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50050002"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="50050002"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:axPos val="l"/>
+        <c:majorGridlines/>
+        <c:title>
+          <c:tx>
+            <c:rich>
+              <a:bodyPr rot="-5400000" vert="horz"/>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:rPr lang="en-US"/>
+                  <a:t>Sale Price (USD)</a:t>
+                </a:r>
+              </a:p>
+            </c:rich>
+          </c:tx>
+          <c:layout/>
+        </c:title>
+        <c:numFmt formatCode="$#,##0" sourceLinked="0"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="50050001"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:srgbClr val="F6FFF0"/>
+    </a:solidFill>
+    <a:ln>
+      <a:solidFill>
+        <a:srgbClr val="A9D18E"/>
+      </a:solidFill>
+    </a:ln>
+  </c:spPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
@@ -1263,6 +4604,36 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>38100</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>676275</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="6" name="Chart 5"/>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2338,10 +5709,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:N501"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
@@ -2366,8 +5737,14 @@
       <c r="K1" s="2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
+      <c r="M1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -2396,8 +5773,14 @@
         <f>INDEX(LookupData!$B$32:$H$36,1,MATCH(Dashboard!$R$32,LookupData!$B$31:$H$31,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="3" spans="1:11">
+      <c r="M2">
+        <v>1400</v>
+      </c>
+      <c r="N2">
+        <v>1600000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
       <c r="A3" t="s">
         <v>9</v>
       </c>
@@ -2426,8 +5809,14 @@
         <f>INDEX(LookupData!$B$32:$H$36,2,MATCH(Dashboard!$R$32,LookupData!$B$31:$H$31,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="4" spans="1:11">
+      <c r="M3">
+        <v>3000</v>
+      </c>
+      <c r="N3">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -2456,8 +5845,14 @@
         <f>INDEX(LookupData!$B$32:$H$36,3,MATCH(Dashboard!$R$32,LookupData!$B$31:$H$31,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:11">
+      <c r="M4">
+        <v>2080</v>
+      </c>
+      <c r="N4">
+        <v>640000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
         <v>11</v>
       </c>
@@ -2486,8 +5881,14 @@
         <f>INDEX(LookupData!$B$32:$H$36,4,MATCH(Dashboard!$R$32,LookupData!$B$31:$H$31,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="6" spans="1:11">
+      <c r="M5">
+        <v>1165</v>
+      </c>
+      <c r="N5">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
         <v>12</v>
       </c>
@@ -2516,8 +5917,14 @@
         <f>INDEX(LookupData!$B$32:$H$36,5,MATCH(Dashboard!$R$32,LookupData!$B$31:$H$31,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:11">
+      <c r="M6">
+        <v>1200</v>
+      </c>
+      <c r="N6">
+        <v>356420</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="D7" t="s">
         <v>18</v>
       </c>
@@ -2532,8 +5939,14 @@
         <f>INDEX(LookupData!$B$24:$G$29,6,MATCH(Dashboard!$F$32,LookupData!$B$23:$G$23,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:11">
+      <c r="M7">
+        <v>5400</v>
+      </c>
+      <c r="N7">
+        <v>2050000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="D8" t="s">
         <v>19</v>
       </c>
@@ -2541,8 +5954,14 @@
         <f>INDEX(LookupData!$B$10:$G$21,7,MATCH(Dashboard!$R$8,LookupData!$B$9:$G$9,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="9" spans="1:11">
+      <c r="M8">
+        <v>1820</v>
+      </c>
+      <c r="N8">
+        <v>570000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="D9" t="s">
         <v>20</v>
       </c>
@@ -2550,8 +5969,14 @@
         <f>INDEX(LookupData!$B$10:$G$21,8,MATCH(Dashboard!$R$8,LookupData!$B$9:$G$9,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:11">
+      <c r="M9">
+        <v>1683</v>
+      </c>
+      <c r="N9">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="D10" t="s">
         <v>21</v>
       </c>
@@ -2559,8 +5984,14 @@
         <f>INDEX(LookupData!$B$10:$G$21,9,MATCH(Dashboard!$R$8,LookupData!$B$9:$G$9,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="11" spans="1:11">
+      <c r="M10">
+        <v>912</v>
+      </c>
+      <c r="N10">
+        <v>505000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="D11" t="s">
         <v>22</v>
       </c>
@@ -2568,8 +5999,14 @@
         <f>INDEX(LookupData!$B$10:$G$21,10,MATCH(Dashboard!$R$8,LookupData!$B$9:$G$9,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:11">
+      <c r="M11">
+        <v>1248</v>
+      </c>
+      <c r="N11">
+        <v>920000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="D12" t="s">
         <v>23</v>
       </c>
@@ -2577,14 +6014,3930 @@
         <f>INDEX(LookupData!$B$10:$G$21,11,MATCH(Dashboard!$R$8,LookupData!$B$9:$G$9,0))</f>
         <v>0</v>
       </c>
-    </row>
-    <row r="13" spans="1:11">
+      <c r="M12">
+        <v>2808</v>
+      </c>
+      <c r="N12">
+        <v>925000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="D13" t="s">
         <v>24</v>
       </c>
       <c r="E13">
         <f>INDEX(LookupData!$B$10:$G$21,12,MATCH(Dashboard!$R$8,LookupData!$B$9:$G$9,0))</f>
         <v>0</v>
+      </c>
+      <c r="M13">
+        <v>1312</v>
+      </c>
+      <c r="N13">
+        <v>758000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="M14">
+        <v>420</v>
+      </c>
+      <c r="N14">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="M15">
+        <v>1264</v>
+      </c>
+      <c r="N15">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="M16">
+        <v>2640</v>
+      </c>
+      <c r="N16">
+        <v>1300000</v>
+      </c>
+    </row>
+    <row r="17" spans="13:14">
+      <c r="M17">
+        <v>1518</v>
+      </c>
+      <c r="N17">
+        <v>959000</v>
+      </c>
+    </row>
+    <row r="18" spans="13:14">
+      <c r="M18">
+        <v>1449</v>
+      </c>
+      <c r="N18">
+        <v>1150000</v>
+      </c>
+    </row>
+    <row r="19" spans="13:14">
+      <c r="M19">
+        <v>3840</v>
+      </c>
+      <c r="N19">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="20" spans="13:14">
+      <c r="M20">
+        <v>2065</v>
+      </c>
+      <c r="N20">
+        <v>615000</v>
+      </c>
+    </row>
+    <row r="21" spans="13:14">
+      <c r="M21">
+        <v>912</v>
+      </c>
+      <c r="N21">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="22" spans="13:14">
+      <c r="M22">
+        <v>1152</v>
+      </c>
+      <c r="N22">
+        <v>740000</v>
+      </c>
+    </row>
+    <row r="23" spans="13:14">
+      <c r="M23">
+        <v>1550</v>
+      </c>
+      <c r="N23">
+        <v>407849</v>
+      </c>
+    </row>
+    <row r="24" spans="13:14">
+      <c r="M24">
+        <v>1050</v>
+      </c>
+      <c r="N24">
+        <v>720000</v>
+      </c>
+    </row>
+    <row r="25" spans="13:14">
+      <c r="M25">
+        <v>1095</v>
+      </c>
+      <c r="N25">
+        <v>760000</v>
+      </c>
+    </row>
+    <row r="26" spans="13:14">
+      <c r="M26">
+        <v>1750</v>
+      </c>
+      <c r="N26">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="27" spans="13:14">
+      <c r="M27">
+        <v>1776</v>
+      </c>
+      <c r="N27">
+        <v>635000</v>
+      </c>
+    </row>
+    <row r="28" spans="13:14">
+      <c r="M28">
+        <v>1526</v>
+      </c>
+      <c r="N28">
+        <v>565000</v>
+      </c>
+    </row>
+    <row r="29" spans="13:14">
+      <c r="M29">
+        <v>918</v>
+      </c>
+      <c r="N29">
+        <v>760000</v>
+      </c>
+    </row>
+    <row r="30" spans="13:14">
+      <c r="M30">
+        <v>1172</v>
+      </c>
+      <c r="N30">
+        <v>360000</v>
+      </c>
+    </row>
+    <row r="31" spans="13:14">
+      <c r="M31">
+        <v>1490</v>
+      </c>
+      <c r="N31">
+        <v>330000</v>
+      </c>
+    </row>
+    <row r="32" spans="13:14">
+      <c r="M32">
+        <v>1152</v>
+      </c>
+      <c r="N32">
+        <v>760000</v>
+      </c>
+    </row>
+    <row r="33" spans="13:14">
+      <c r="M33">
+        <v>879</v>
+      </c>
+      <c r="N33">
+        <v>485000</v>
+      </c>
+    </row>
+    <row r="34" spans="13:14">
+      <c r="M34">
+        <v>2400</v>
+      </c>
+      <c r="N34">
+        <v>965000</v>
+      </c>
+    </row>
+    <row r="35" spans="13:14">
+      <c r="M35">
+        <v>2034</v>
+      </c>
+      <c r="N35">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="36" spans="13:14">
+      <c r="M36">
+        <v>1936</v>
+      </c>
+      <c r="N36">
+        <v>630000</v>
+      </c>
+    </row>
+    <row r="37" spans="13:14">
+      <c r="M37">
+        <v>1170</v>
+      </c>
+      <c r="N37">
+        <v>365000</v>
+      </c>
+    </row>
+    <row r="38" spans="13:14">
+      <c r="M38">
+        <v>2524</v>
+      </c>
+      <c r="N38">
+        <v>1135000</v>
+      </c>
+    </row>
+    <row r="39" spans="13:14">
+      <c r="M39">
+        <v>1706</v>
+      </c>
+      <c r="N39">
+        <v>1722800</v>
+      </c>
+    </row>
+    <row r="40" spans="13:14">
+      <c r="M40">
+        <v>924</v>
+      </c>
+      <c r="N40">
+        <v>436000</v>
+      </c>
+    </row>
+    <row r="41" spans="13:14">
+      <c r="M41">
+        <v>2520</v>
+      </c>
+      <c r="N41">
+        <v>625000</v>
+      </c>
+    </row>
+    <row r="42" spans="13:14">
+      <c r="M42">
+        <v>1470</v>
+      </c>
+      <c r="N42">
+        <v>775000</v>
+      </c>
+    </row>
+    <row r="43" spans="13:14">
+      <c r="M43">
+        <v>2590</v>
+      </c>
+      <c r="N43">
+        <v>870000</v>
+      </c>
+    </row>
+    <row r="44" spans="13:14">
+      <c r="M44">
+        <v>1472</v>
+      </c>
+      <c r="N44">
+        <v>590000</v>
+      </c>
+    </row>
+    <row r="45" spans="13:14">
+      <c r="M45">
+        <v>1440</v>
+      </c>
+      <c r="N45">
+        <v>668000</v>
+      </c>
+    </row>
+    <row r="46" spans="13:14">
+      <c r="M46">
+        <v>1890</v>
+      </c>
+      <c r="N46">
+        <v>670000</v>
+      </c>
+    </row>
+    <row r="47" spans="13:14">
+      <c r="M47">
+        <v>1440</v>
+      </c>
+      <c r="N47">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="48" spans="13:14">
+      <c r="M48">
+        <v>816</v>
+      </c>
+      <c r="N48">
+        <v>495000</v>
+      </c>
+    </row>
+    <row r="49" spans="13:14">
+      <c r="M49">
+        <v>3280</v>
+      </c>
+      <c r="N49">
+        <v>705000</v>
+      </c>
+    </row>
+    <row r="50" spans="13:14">
+      <c r="M50">
+        <v>1268</v>
+      </c>
+      <c r="N50">
+        <v>390000</v>
+      </c>
+    </row>
+    <row r="51" spans="13:14">
+      <c r="M51">
+        <v>1380</v>
+      </c>
+      <c r="N51">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="52" spans="13:14">
+      <c r="M52">
+        <v>1273</v>
+      </c>
+      <c r="N52">
+        <v>903000</v>
+      </c>
+    </row>
+    <row r="53" spans="13:14">
+      <c r="M53">
+        <v>1944</v>
+      </c>
+      <c r="N53">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="54" spans="13:14">
+      <c r="M54">
+        <v>1612</v>
+      </c>
+      <c r="N54">
+        <v>660000</v>
+      </c>
+    </row>
+    <row r="55" spans="13:14">
+      <c r="M55">
+        <v>1680</v>
+      </c>
+      <c r="N55">
+        <v>1355000</v>
+      </c>
+    </row>
+    <row r="56" spans="13:14">
+      <c r="M56">
+        <v>884</v>
+      </c>
+      <c r="N56">
+        <v>329000</v>
+      </c>
+    </row>
+    <row r="57" spans="13:14">
+      <c r="M57">
+        <v>1188</v>
+      </c>
+      <c r="N57">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="58" spans="13:14">
+      <c r="M58">
+        <v>1408</v>
+      </c>
+      <c r="N58">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="59" spans="13:14">
+      <c r="M59">
+        <v>2002</v>
+      </c>
+      <c r="N59">
+        <v>579000</v>
+      </c>
+    </row>
+    <row r="60" spans="13:14">
+      <c r="M60">
+        <v>2970</v>
+      </c>
+      <c r="N60">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="61" spans="13:14">
+      <c r="M61">
+        <v>1440</v>
+      </c>
+      <c r="N61">
+        <v>476000</v>
+      </c>
+    </row>
+    <row r="62" spans="13:14">
+      <c r="M62">
+        <v>2125</v>
+      </c>
+      <c r="N62">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="63" spans="13:14">
+      <c r="M63">
+        <v>2010</v>
+      </c>
+      <c r="N63">
+        <v>465000</v>
+      </c>
+    </row>
+    <row r="64" spans="13:14">
+      <c r="M64">
+        <v>1216</v>
+      </c>
+      <c r="N64">
+        <v>608000</v>
+      </c>
+    </row>
+    <row r="65" spans="13:14">
+      <c r="M65">
+        <v>2280</v>
+      </c>
+      <c r="N65">
+        <v>975000</v>
+      </c>
+    </row>
+    <row r="66" spans="13:14">
+      <c r="M66">
+        <v>1280</v>
+      </c>
+      <c r="N66">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="67" spans="13:14">
+      <c r="M67">
+        <v>1600</v>
+      </c>
+      <c r="N67">
+        <v>576000</v>
+      </c>
+    </row>
+    <row r="68" spans="13:14">
+      <c r="M68">
+        <v>2080</v>
+      </c>
+      <c r="N68">
+        <v>698298</v>
+      </c>
+    </row>
+    <row r="69" spans="13:14">
+      <c r="M69">
+        <v>1800</v>
+      </c>
+      <c r="N69">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="70" spans="13:14">
+      <c r="M70">
+        <v>1919</v>
+      </c>
+      <c r="N70">
+        <v>495500</v>
+      </c>
+    </row>
+    <row r="71" spans="13:14">
+      <c r="M71">
+        <v>1652</v>
+      </c>
+      <c r="N71">
+        <v>486720</v>
+      </c>
+    </row>
+    <row r="72" spans="13:14">
+      <c r="M72">
+        <v>2500</v>
+      </c>
+      <c r="N72">
+        <v>980000</v>
+      </c>
+    </row>
+    <row r="73" spans="13:14">
+      <c r="M73">
+        <v>1690</v>
+      </c>
+      <c r="N73">
+        <v>365000</v>
+      </c>
+    </row>
+    <row r="74" spans="13:14">
+      <c r="M74">
+        <v>2280</v>
+      </c>
+      <c r="N74">
+        <v>1230000</v>
+      </c>
+    </row>
+    <row r="75" spans="13:14">
+      <c r="M75">
+        <v>2192</v>
+      </c>
+      <c r="N75">
+        <v>135000</v>
+      </c>
+    </row>
+    <row r="76" spans="13:14">
+      <c r="M76">
+        <v>2280</v>
+      </c>
+      <c r="N76">
+        <v>425000</v>
+      </c>
+    </row>
+    <row r="77" spans="13:14">
+      <c r="M77">
+        <v>1352</v>
+      </c>
+      <c r="N77">
+        <v>760000</v>
+      </c>
+    </row>
+    <row r="78" spans="13:14">
+      <c r="M78">
+        <v>906</v>
+      </c>
+      <c r="N78">
+        <v>442000</v>
+      </c>
+    </row>
+    <row r="79" spans="13:14">
+      <c r="M79">
+        <v>2040</v>
+      </c>
+      <c r="N79">
+        <v>425000</v>
+      </c>
+    </row>
+    <row r="80" spans="13:14">
+      <c r="M80">
+        <v>1975</v>
+      </c>
+      <c r="N80">
+        <v>927000</v>
+      </c>
+    </row>
+    <row r="81" spans="13:14">
+      <c r="M81">
+        <v>1444</v>
+      </c>
+      <c r="N81">
+        <v>640000</v>
+      </c>
+    </row>
+    <row r="82" spans="13:14">
+      <c r="M82">
+        <v>3600</v>
+      </c>
+      <c r="N82">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="83" spans="13:14">
+      <c r="M83">
+        <v>1672</v>
+      </c>
+      <c r="N83">
+        <v>261250</v>
+      </c>
+    </row>
+    <row r="84" spans="13:14">
+      <c r="M84">
+        <v>1680</v>
+      </c>
+      <c r="N84">
+        <v>685000</v>
+      </c>
+    </row>
+    <row r="85" spans="13:14">
+      <c r="M85">
+        <v>1400</v>
+      </c>
+      <c r="N85">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="86" spans="13:14">
+      <c r="M86">
+        <v>2160</v>
+      </c>
+      <c r="N86">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="87" spans="13:14">
+      <c r="M87">
+        <v>1282</v>
+      </c>
+      <c r="N87">
+        <v>720000</v>
+      </c>
+    </row>
+    <row r="88" spans="13:14">
+      <c r="M88">
+        <v>1150</v>
+      </c>
+      <c r="N88">
+        <v>570000</v>
+      </c>
+    </row>
+    <row r="89" spans="13:14">
+      <c r="M89">
+        <v>2254</v>
+      </c>
+      <c r="N89">
+        <v>680000</v>
+      </c>
+    </row>
+    <row r="90" spans="13:14">
+      <c r="M90">
+        <v>1342</v>
+      </c>
+      <c r="N90">
+        <v>640000</v>
+      </c>
+    </row>
+    <row r="91" spans="13:14">
+      <c r="M91">
+        <v>1955</v>
+      </c>
+      <c r="N91">
+        <v>815000</v>
+      </c>
+    </row>
+    <row r="92" spans="13:14">
+      <c r="M92">
+        <v>1118</v>
+      </c>
+      <c r="N92">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="93" spans="13:14">
+      <c r="M93">
+        <v>1998</v>
+      </c>
+      <c r="N93">
+        <v>540000</v>
+      </c>
+    </row>
+    <row r="94" spans="13:14">
+      <c r="M94">
+        <v>1056</v>
+      </c>
+      <c r="N94">
+        <v>390000</v>
+      </c>
+    </row>
+    <row r="95" spans="13:14">
+      <c r="M95">
+        <v>1870</v>
+      </c>
+      <c r="N95">
+        <v>374166</v>
+      </c>
+    </row>
+    <row r="96" spans="13:14">
+      <c r="M96">
+        <v>1232</v>
+      </c>
+      <c r="N96">
+        <v>520000</v>
+      </c>
+    </row>
+    <row r="97" spans="13:14">
+      <c r="M97">
+        <v>1300</v>
+      </c>
+      <c r="N97">
+        <v>905000</v>
+      </c>
+    </row>
+    <row r="98" spans="13:14">
+      <c r="M98">
+        <v>1240</v>
+      </c>
+      <c r="N98">
+        <v>475000</v>
+      </c>
+    </row>
+    <row r="99" spans="13:14">
+      <c r="M99">
+        <v>2108</v>
+      </c>
+      <c r="N99">
+        <v>710000</v>
+      </c>
+    </row>
+    <row r="100" spans="13:14">
+      <c r="M100">
+        <v>2020</v>
+      </c>
+      <c r="N100">
+        <v>775000</v>
+      </c>
+    </row>
+    <row r="101" spans="13:14">
+      <c r="M101">
+        <v>3795</v>
+      </c>
+      <c r="N101">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="102" spans="13:14">
+      <c r="M102">
+        <v>1551</v>
+      </c>
+      <c r="N102">
+        <v>475000</v>
+      </c>
+    </row>
+    <row r="103" spans="13:14">
+      <c r="M103">
+        <v>3510</v>
+      </c>
+      <c r="N103">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="104" spans="13:14">
+      <c r="M104">
+        <v>1536</v>
+      </c>
+      <c r="N104">
+        <v>645000</v>
+      </c>
+    </row>
+    <row r="105" spans="13:14">
+      <c r="M105">
+        <v>960</v>
+      </c>
+      <c r="N105">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="106" spans="13:14">
+      <c r="M106">
+        <v>2180</v>
+      </c>
+      <c r="N106">
+        <v>525000</v>
+      </c>
+    </row>
+    <row r="107" spans="13:14">
+      <c r="M107">
+        <v>1490</v>
+      </c>
+      <c r="N107">
+        <v>840000</v>
+      </c>
+    </row>
+    <row r="108" spans="13:14">
+      <c r="M108">
+        <v>1432</v>
+      </c>
+      <c r="N108">
+        <v>920000</v>
+      </c>
+    </row>
+    <row r="109" spans="13:14">
+      <c r="M109">
+        <v>1275</v>
+      </c>
+      <c r="N109">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="110" spans="13:14">
+      <c r="M110">
+        <v>1472</v>
+      </c>
+      <c r="N110">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="111" spans="13:14">
+      <c r="M111">
+        <v>3336</v>
+      </c>
+      <c r="N111">
+        <v>999000</v>
+      </c>
+    </row>
+    <row r="112" spans="13:14">
+      <c r="M112">
+        <v>3120</v>
+      </c>
+      <c r="N112">
+        <v>1760000</v>
+      </c>
+    </row>
+    <row r="113" spans="13:14">
+      <c r="M113">
+        <v>990</v>
+      </c>
+      <c r="N113">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="114" spans="13:14">
+      <c r="M114">
+        <v>2425</v>
+      </c>
+      <c r="N114">
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="115" spans="13:14">
+      <c r="M115">
+        <v>2604</v>
+      </c>
+      <c r="N115">
+        <v>381250</v>
+      </c>
+    </row>
+    <row r="116" spans="13:14">
+      <c r="M116">
+        <v>2640</v>
+      </c>
+      <c r="N116">
+        <v>275000</v>
+      </c>
+    </row>
+    <row r="117" spans="13:14">
+      <c r="M117">
+        <v>872</v>
+      </c>
+      <c r="N117">
+        <v>515000</v>
+      </c>
+    </row>
+    <row r="118" spans="13:14">
+      <c r="M118">
+        <v>2100</v>
+      </c>
+      <c r="N118">
+        <v>460000</v>
+      </c>
+    </row>
+    <row r="119" spans="13:14">
+      <c r="M119">
+        <v>1170</v>
+      </c>
+      <c r="N119">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="120" spans="13:14">
+      <c r="M120">
+        <v>2360</v>
+      </c>
+      <c r="N120">
+        <v>795000</v>
+      </c>
+    </row>
+    <row r="121" spans="13:14">
+      <c r="M121">
+        <v>1496</v>
+      </c>
+      <c r="N121">
+        <v>1440000</v>
+      </c>
+    </row>
+    <row r="122" spans="13:14">
+      <c r="M122">
+        <v>2000</v>
+      </c>
+      <c r="N122">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="123" spans="13:14">
+      <c r="M123">
+        <v>4608</v>
+      </c>
+      <c r="N123">
+        <v>9900000</v>
+      </c>
+    </row>
+    <row r="124" spans="13:14">
+      <c r="M124">
+        <v>5244</v>
+      </c>
+      <c r="N124">
+        <v>3150000</v>
+      </c>
+    </row>
+    <row r="125" spans="13:14">
+      <c r="M125">
+        <v>3040</v>
+      </c>
+      <c r="N125">
+        <v>165000</v>
+      </c>
+    </row>
+    <row r="126" spans="13:14">
+      <c r="M126">
+        <v>2130</v>
+      </c>
+      <c r="N126">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="127" spans="13:14">
+      <c r="M127">
+        <v>2280</v>
+      </c>
+      <c r="N127">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="128" spans="13:14">
+      <c r="M128">
+        <v>1172</v>
+      </c>
+      <c r="N128">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="129" spans="13:14">
+      <c r="M129">
+        <v>3420</v>
+      </c>
+      <c r="N129">
+        <v>1250000</v>
+      </c>
+    </row>
+    <row r="130" spans="13:14">
+      <c r="M130">
+        <v>3280</v>
+      </c>
+      <c r="N130">
+        <v>786500</v>
+      </c>
+    </row>
+    <row r="131" spans="13:14">
+      <c r="M131">
+        <v>1122</v>
+      </c>
+      <c r="N131">
+        <v>768000</v>
+      </c>
+    </row>
+    <row r="132" spans="13:14">
+      <c r="M132">
+        <v>2113</v>
+      </c>
+      <c r="N132">
+        <v>880000</v>
+      </c>
+    </row>
+    <row r="133" spans="13:14">
+      <c r="M133">
+        <v>1224</v>
+      </c>
+      <c r="N133">
+        <v>1090000</v>
+      </c>
+    </row>
+    <row r="134" spans="13:14">
+      <c r="M134">
+        <v>2208</v>
+      </c>
+      <c r="N134">
+        <v>180000</v>
+      </c>
+    </row>
+    <row r="135" spans="13:14">
+      <c r="M135">
+        <v>1900</v>
+      </c>
+      <c r="N135">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="136" spans="13:14">
+      <c r="M136">
+        <v>1222</v>
+      </c>
+      <c r="N136">
+        <v>515000</v>
+      </c>
+    </row>
+    <row r="137" spans="13:14">
+      <c r="M137">
+        <v>1764</v>
+      </c>
+      <c r="N137">
+        <v>545000</v>
+      </c>
+    </row>
+    <row r="138" spans="13:14">
+      <c r="M138">
+        <v>2892</v>
+      </c>
+      <c r="N138">
+        <v>1180000</v>
+      </c>
+    </row>
+    <row r="139" spans="13:14">
+      <c r="M139">
+        <v>1496</v>
+      </c>
+      <c r="N139">
+        <v>728000</v>
+      </c>
+    </row>
+    <row r="140" spans="13:14">
+      <c r="M140">
+        <v>1354</v>
+      </c>
+      <c r="N140">
+        <v>295000</v>
+      </c>
+    </row>
+    <row r="141" spans="13:14">
+      <c r="M141">
+        <v>1272</v>
+      </c>
+      <c r="N141">
+        <v>410000</v>
+      </c>
+    </row>
+    <row r="142" spans="13:14">
+      <c r="M142">
+        <v>1324</v>
+      </c>
+      <c r="N142">
+        <v>715000</v>
+      </c>
+    </row>
+    <row r="143" spans="13:14">
+      <c r="M143">
+        <v>1568</v>
+      </c>
+      <c r="N143">
+        <v>589000</v>
+      </c>
+    </row>
+    <row r="144" spans="13:14">
+      <c r="M144">
+        <v>1456</v>
+      </c>
+      <c r="N144">
+        <v>915000</v>
+      </c>
+    </row>
+    <row r="145" spans="13:14">
+      <c r="M145">
+        <v>3553</v>
+      </c>
+      <c r="N145">
+        <v>1362000</v>
+      </c>
+    </row>
+    <row r="146" spans="13:14">
+      <c r="M146">
+        <v>2078</v>
+      </c>
+      <c r="N146">
+        <v>643400</v>
+      </c>
+    </row>
+    <row r="147" spans="13:14">
+      <c r="M147">
+        <v>810</v>
+      </c>
+      <c r="N147">
+        <v>265000</v>
+      </c>
+    </row>
+    <row r="148" spans="13:14">
+      <c r="M148">
+        <v>1624</v>
+      </c>
+      <c r="N148">
+        <v>995000</v>
+      </c>
+    </row>
+    <row r="149" spans="13:14">
+      <c r="M149">
+        <v>2044</v>
+      </c>
+      <c r="N149">
+        <v>895000</v>
+      </c>
+    </row>
+    <row r="150" spans="13:14">
+      <c r="M150">
+        <v>2160</v>
+      </c>
+      <c r="N150">
+        <v>595000</v>
+      </c>
+    </row>
+    <row r="151" spans="13:14">
+      <c r="M151">
+        <v>2120</v>
+      </c>
+      <c r="N151">
+        <v>890000</v>
+      </c>
+    </row>
+    <row r="152" spans="13:14">
+      <c r="M152">
+        <v>2904</v>
+      </c>
+      <c r="N152">
+        <v>1430000</v>
+      </c>
+    </row>
+    <row r="153" spans="13:14">
+      <c r="M153">
+        <v>1920</v>
+      </c>
+      <c r="N153">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="154" spans="13:14">
+      <c r="M154">
+        <v>2350</v>
+      </c>
+      <c r="N154">
+        <v>689000</v>
+      </c>
+    </row>
+    <row r="155" spans="13:14">
+      <c r="M155">
+        <v>1592</v>
+      </c>
+      <c r="N155">
+        <v>573000</v>
+      </c>
+    </row>
+    <row r="156" spans="13:14">
+      <c r="M156">
+        <v>1680</v>
+      </c>
+      <c r="N156">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="157" spans="13:14">
+      <c r="M157">
+        <v>944</v>
+      </c>
+      <c r="N157">
+        <v>405000</v>
+      </c>
+    </row>
+    <row r="158" spans="13:14">
+      <c r="M158">
+        <v>2880</v>
+      </c>
+      <c r="N158">
+        <v>4600000</v>
+      </c>
+    </row>
+    <row r="159" spans="13:14">
+      <c r="M159">
+        <v>988</v>
+      </c>
+      <c r="N159">
+        <v>429000</v>
+      </c>
+    </row>
+    <row r="160" spans="13:14">
+      <c r="M160">
+        <v>3496</v>
+      </c>
+      <c r="N160">
+        <v>5650000</v>
+      </c>
+    </row>
+    <row r="161" spans="13:14">
+      <c r="M161">
+        <v>4852</v>
+      </c>
+      <c r="N161">
+        <v>3300000</v>
+      </c>
+    </row>
+    <row r="162" spans="13:14">
+      <c r="M162">
+        <v>1360</v>
+      </c>
+      <c r="N162">
+        <v>525000</v>
+      </c>
+    </row>
+    <row r="163" spans="13:14">
+      <c r="M163">
+        <v>1434</v>
+      </c>
+      <c r="N163">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="164" spans="13:14">
+      <c r="M164">
+        <v>942</v>
+      </c>
+      <c r="N164">
+        <v>890968</v>
+      </c>
+    </row>
+    <row r="165" spans="13:14">
+      <c r="M165">
+        <v>1760</v>
+      </c>
+      <c r="N165">
+        <v>562000</v>
+      </c>
+    </row>
+    <row r="166" spans="13:14">
+      <c r="M166">
+        <v>3000</v>
+      </c>
+      <c r="N166">
+        <v>42500</v>
+      </c>
+    </row>
+    <row r="167" spans="13:14">
+      <c r="M167">
+        <v>1512</v>
+      </c>
+      <c r="N167">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="168" spans="13:14">
+      <c r="M168">
+        <v>2510</v>
+      </c>
+      <c r="N168">
+        <v>1150000</v>
+      </c>
+    </row>
+    <row r="169" spans="13:14">
+      <c r="M169">
+        <v>3120</v>
+      </c>
+      <c r="N169">
+        <v>528000</v>
+      </c>
+    </row>
+    <row r="170" spans="13:14">
+      <c r="M170">
+        <v>3348</v>
+      </c>
+      <c r="N170">
+        <v>266600</v>
+      </c>
+    </row>
+    <row r="171" spans="13:14">
+      <c r="M171">
+        <v>1348</v>
+      </c>
+      <c r="N171">
+        <v>316863</v>
+      </c>
+    </row>
+    <row r="172" spans="13:14">
+      <c r="M172">
+        <v>1440</v>
+      </c>
+      <c r="N172">
+        <v>389000</v>
+      </c>
+    </row>
+    <row r="173" spans="13:14">
+      <c r="M173">
+        <v>1136</v>
+      </c>
+      <c r="N173">
+        <v>498000</v>
+      </c>
+    </row>
+    <row r="174" spans="13:14">
+      <c r="M174">
+        <v>1936</v>
+      </c>
+      <c r="N174">
+        <v>675000</v>
+      </c>
+    </row>
+    <row r="175" spans="13:14">
+      <c r="M175">
+        <v>1506</v>
+      </c>
+      <c r="N175">
+        <v>540000</v>
+      </c>
+    </row>
+    <row r="176" spans="13:14">
+      <c r="M176">
+        <v>1256</v>
+      </c>
+      <c r="N176">
+        <v>668000</v>
+      </c>
+    </row>
+    <row r="177" spans="13:14">
+      <c r="M177">
+        <v>3400</v>
+      </c>
+      <c r="N177">
+        <v>999000</v>
+      </c>
+    </row>
+    <row r="178" spans="13:14">
+      <c r="M178">
+        <v>1080</v>
+      </c>
+      <c r="N178">
+        <v>710000</v>
+      </c>
+    </row>
+    <row r="179" spans="13:14">
+      <c r="M179">
+        <v>1760</v>
+      </c>
+      <c r="N179">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="180" spans="13:14">
+      <c r="M180">
+        <v>3403</v>
+      </c>
+      <c r="N180">
+        <v>525000</v>
+      </c>
+    </row>
+    <row r="181" spans="13:14">
+      <c r="M181">
+        <v>1536</v>
+      </c>
+      <c r="N181">
+        <v>1080000</v>
+      </c>
+    </row>
+    <row r="182" spans="13:14">
+      <c r="M182">
+        <v>2638</v>
+      </c>
+      <c r="N182">
+        <v>1575000</v>
+      </c>
+    </row>
+    <row r="183" spans="13:14">
+      <c r="M183">
+        <v>1120</v>
+      </c>
+      <c r="N183">
+        <v>310000</v>
+      </c>
+    </row>
+    <row r="184" spans="13:14">
+      <c r="M184">
+        <v>1833</v>
+      </c>
+      <c r="N184">
+        <v>570000</v>
+      </c>
+    </row>
+    <row r="185" spans="13:14">
+      <c r="M185">
+        <v>1000</v>
+      </c>
+      <c r="N185">
+        <v>291000</v>
+      </c>
+    </row>
+    <row r="186" spans="13:14">
+      <c r="M186">
+        <v>1565</v>
+      </c>
+      <c r="N186">
+        <v>1325000</v>
+      </c>
+    </row>
+    <row r="187" spans="13:14">
+      <c r="M187">
+        <v>1931</v>
+      </c>
+      <c r="N187">
+        <v>660000</v>
+      </c>
+    </row>
+    <row r="188" spans="13:14">
+      <c r="M188">
+        <v>1254</v>
+      </c>
+      <c r="N188">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="189" spans="13:14">
+      <c r="M189">
+        <v>2156</v>
+      </c>
+      <c r="N189">
+        <v>515000</v>
+      </c>
+    </row>
+    <row r="190" spans="13:14">
+      <c r="M190">
+        <v>1820</v>
+      </c>
+      <c r="N190">
+        <v>327500</v>
+      </c>
+    </row>
+    <row r="191" spans="13:14">
+      <c r="M191">
+        <v>3078</v>
+      </c>
+      <c r="N191">
+        <v>675000</v>
+      </c>
+    </row>
+    <row r="192" spans="13:14">
+      <c r="M192">
+        <v>1728</v>
+      </c>
+      <c r="N192">
+        <v>1753110</v>
+      </c>
+    </row>
+    <row r="193" spans="13:14">
+      <c r="M193">
+        <v>2248</v>
+      </c>
+      <c r="N193">
+        <v>286000</v>
+      </c>
+    </row>
+    <row r="194" spans="13:14">
+      <c r="M194">
+        <v>3256</v>
+      </c>
+      <c r="N194">
+        <v>1633333</v>
+      </c>
+    </row>
+    <row r="195" spans="13:14">
+      <c r="M195">
+        <v>1664</v>
+      </c>
+      <c r="N195">
+        <v>250000</v>
+      </c>
+    </row>
+    <row r="196" spans="13:14">
+      <c r="M196">
+        <v>1631</v>
+      </c>
+      <c r="N196">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="197" spans="13:14">
+      <c r="M197">
+        <v>4435</v>
+      </c>
+      <c r="N197">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="198" spans="13:14">
+      <c r="M198">
+        <v>2350</v>
+      </c>
+      <c r="N198">
+        <v>680000</v>
+      </c>
+    </row>
+    <row r="199" spans="13:14">
+      <c r="M199">
+        <v>1408</v>
+      </c>
+      <c r="N199">
+        <v>1050000</v>
+      </c>
+    </row>
+    <row r="200" spans="13:14">
+      <c r="M200">
+        <v>2480</v>
+      </c>
+      <c r="N200">
+        <v>1360000</v>
+      </c>
+    </row>
+    <row r="201" spans="13:14">
+      <c r="M201">
+        <v>1292</v>
+      </c>
+      <c r="N201">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="202" spans="13:14">
+      <c r="M202">
+        <v>1008</v>
+      </c>
+      <c r="N202">
+        <v>225000</v>
+      </c>
+    </row>
+    <row r="203" spans="13:14">
+      <c r="M203">
+        <v>1650</v>
+      </c>
+      <c r="N203">
+        <v>435000</v>
+      </c>
+    </row>
+    <row r="204" spans="13:14">
+      <c r="M204">
+        <v>2016</v>
+      </c>
+      <c r="N204">
+        <v>310000</v>
+      </c>
+    </row>
+    <row r="205" spans="13:14">
+      <c r="M205">
+        <v>1800</v>
+      </c>
+      <c r="N205">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="206" spans="13:14">
+      <c r="M206">
+        <v>2391</v>
+      </c>
+      <c r="N206">
+        <v>790000</v>
+      </c>
+    </row>
+    <row r="207" spans="13:14">
+      <c r="M207">
+        <v>896</v>
+      </c>
+      <c r="N207">
+        <v>670000</v>
+      </c>
+    </row>
+    <row r="208" spans="13:14">
+      <c r="M208">
+        <v>2952</v>
+      </c>
+      <c r="N208">
+        <v>415000</v>
+      </c>
+    </row>
+    <row r="209" spans="13:14">
+      <c r="M209">
+        <v>3604</v>
+      </c>
+      <c r="N209">
+        <v>323534</v>
+      </c>
+    </row>
+    <row r="210" spans="13:14">
+      <c r="M210">
+        <v>1616</v>
+      </c>
+      <c r="N210">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="211" spans="13:14">
+      <c r="M211">
+        <v>3720</v>
+      </c>
+      <c r="N211">
+        <v>1500000</v>
+      </c>
+    </row>
+    <row r="212" spans="13:14">
+      <c r="M212">
+        <v>980</v>
+      </c>
+      <c r="N212">
+        <v>305000</v>
+      </c>
+    </row>
+    <row r="213" spans="13:14">
+      <c r="M213">
+        <v>1008</v>
+      </c>
+      <c r="N213">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="214" spans="13:14">
+      <c r="M214">
+        <v>1836</v>
+      </c>
+      <c r="N214">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="215" spans="13:14">
+      <c r="M215">
+        <v>1296</v>
+      </c>
+      <c r="N215">
+        <v>390000</v>
+      </c>
+    </row>
+    <row r="216" spans="13:14">
+      <c r="M216">
+        <v>2250</v>
+      </c>
+      <c r="N216">
+        <v>845000</v>
+      </c>
+    </row>
+    <row r="217" spans="13:14">
+      <c r="M217">
+        <v>1962</v>
+      </c>
+      <c r="N217">
+        <v>790000</v>
+      </c>
+    </row>
+    <row r="218" spans="13:14">
+      <c r="M218">
+        <v>1800</v>
+      </c>
+      <c r="N218">
+        <v>790000</v>
+      </c>
+    </row>
+    <row r="219" spans="13:14">
+      <c r="M219">
+        <v>1254</v>
+      </c>
+      <c r="N219">
+        <v>497800</v>
+      </c>
+    </row>
+    <row r="220" spans="13:14">
+      <c r="M220">
+        <v>5400</v>
+      </c>
+      <c r="N220">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="221" spans="13:14">
+      <c r="M221">
+        <v>1360</v>
+      </c>
+      <c r="N221">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="222" spans="13:14">
+      <c r="M222">
+        <v>2600</v>
+      </c>
+      <c r="N222">
+        <v>572000</v>
+      </c>
+    </row>
+    <row r="223" spans="13:14">
+      <c r="M223">
+        <v>3700</v>
+      </c>
+      <c r="N223">
+        <v>7090000</v>
+      </c>
+    </row>
+    <row r="224" spans="13:14">
+      <c r="M224">
+        <v>2100</v>
+      </c>
+      <c r="N224">
+        <v>1230000</v>
+      </c>
+    </row>
+    <row r="225" spans="13:14">
+      <c r="M225">
+        <v>1224</v>
+      </c>
+      <c r="N225">
+        <v>1270000</v>
+      </c>
+    </row>
+    <row r="226" spans="13:14">
+      <c r="M226">
+        <v>1320</v>
+      </c>
+      <c r="N226">
+        <v>539000</v>
+      </c>
+    </row>
+    <row r="227" spans="13:14">
+      <c r="M227">
+        <v>1469</v>
+      </c>
+      <c r="N227">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="228" spans="13:14">
+      <c r="M228">
+        <v>800</v>
+      </c>
+      <c r="N228">
+        <v>379000</v>
+      </c>
+    </row>
+    <row r="229" spans="13:14">
+      <c r="M229">
+        <v>1398</v>
+      </c>
+      <c r="N229">
+        <v>610000</v>
+      </c>
+    </row>
+    <row r="230" spans="13:14">
+      <c r="M230">
+        <v>3150</v>
+      </c>
+      <c r="N230">
+        <v>335000</v>
+      </c>
+    </row>
+    <row r="231" spans="13:14">
+      <c r="M231">
+        <v>1008</v>
+      </c>
+      <c r="N231">
+        <v>820000</v>
+      </c>
+    </row>
+    <row r="232" spans="13:14">
+      <c r="M232">
+        <v>5475</v>
+      </c>
+      <c r="N232">
+        <v>1421175</v>
+      </c>
+    </row>
+    <row r="233" spans="13:14">
+      <c r="M233">
+        <v>1813</v>
+      </c>
+      <c r="N233">
+        <v>590000</v>
+      </c>
+    </row>
+    <row r="234" spans="13:14">
+      <c r="M234">
+        <v>2240</v>
+      </c>
+      <c r="N234">
+        <v>228500</v>
+      </c>
+    </row>
+    <row r="235" spans="13:14">
+      <c r="M235">
+        <v>1785</v>
+      </c>
+      <c r="N235">
+        <v>720000</v>
+      </c>
+    </row>
+    <row r="236" spans="13:14">
+      <c r="M236">
+        <v>2052</v>
+      </c>
+      <c r="N236">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="237" spans="13:14">
+      <c r="M237">
+        <v>2160</v>
+      </c>
+      <c r="N237">
+        <v>1300000</v>
+      </c>
+    </row>
+    <row r="238" spans="13:14">
+      <c r="M238">
+        <v>1155</v>
+      </c>
+      <c r="N238">
+        <v>655000</v>
+      </c>
+    </row>
+    <row r="239" spans="13:14">
+      <c r="M239">
+        <v>4400</v>
+      </c>
+      <c r="N239">
+        <v>479838</v>
+      </c>
+    </row>
+    <row r="240" spans="13:14">
+      <c r="M240">
+        <v>1620</v>
+      </c>
+      <c r="N240">
+        <v>1472074</v>
+      </c>
+    </row>
+    <row r="241" spans="13:14">
+      <c r="M241">
+        <v>3300</v>
+      </c>
+      <c r="N241">
+        <v>998500</v>
+      </c>
+    </row>
+    <row r="242" spans="13:14">
+      <c r="M242">
+        <v>1620</v>
+      </c>
+      <c r="N242">
+        <v>385000</v>
+      </c>
+    </row>
+    <row r="243" spans="13:14">
+      <c r="M243">
+        <v>1280</v>
+      </c>
+      <c r="N243">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="244" spans="13:14">
+      <c r="M244">
+        <v>1200</v>
+      </c>
+      <c r="N244">
+        <v>441090</v>
+      </c>
+    </row>
+    <row r="245" spans="13:14">
+      <c r="M245">
+        <v>1120</v>
+      </c>
+      <c r="N245">
+        <v>485000</v>
+      </c>
+    </row>
+    <row r="246" spans="13:14">
+      <c r="M246">
+        <v>1272</v>
+      </c>
+      <c r="N246">
+        <v>892000</v>
+      </c>
+    </row>
+    <row r="247" spans="13:14">
+      <c r="M247">
+        <v>2380</v>
+      </c>
+      <c r="N247">
+        <v>230000</v>
+      </c>
+    </row>
+    <row r="248" spans="13:14">
+      <c r="M248">
+        <v>1851</v>
+      </c>
+      <c r="N248">
+        <v>710000</v>
+      </c>
+    </row>
+    <row r="249" spans="13:14">
+      <c r="M249">
+        <v>1936</v>
+      </c>
+      <c r="N249">
+        <v>935000</v>
+      </c>
+    </row>
+    <row r="250" spans="13:14">
+      <c r="M250">
+        <v>2700</v>
+      </c>
+      <c r="N250">
+        <v>855000</v>
+      </c>
+    </row>
+    <row r="251" spans="13:14">
+      <c r="M251">
+        <v>1217</v>
+      </c>
+      <c r="N251">
+        <v>95000</v>
+      </c>
+    </row>
+    <row r="252" spans="13:14">
+      <c r="M252">
+        <v>1176</v>
+      </c>
+      <c r="N252">
+        <v>445000</v>
+      </c>
+    </row>
+    <row r="253" spans="13:14">
+      <c r="M253">
+        <v>1332</v>
+      </c>
+      <c r="N253">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="254" spans="13:14">
+      <c r="M254">
+        <v>1408</v>
+      </c>
+      <c r="N254">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="255" spans="13:14">
+      <c r="M255">
+        <v>2710</v>
+      </c>
+      <c r="N255">
+        <v>162500</v>
+      </c>
+    </row>
+    <row r="256" spans="13:14">
+      <c r="M256">
+        <v>2597</v>
+      </c>
+      <c r="N256">
+        <v>1388888</v>
+      </c>
+    </row>
+    <row r="257" spans="13:14">
+      <c r="M257">
+        <v>1500</v>
+      </c>
+      <c r="N257">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="258" spans="13:14">
+      <c r="M258">
+        <v>2700</v>
+      </c>
+      <c r="N258">
+        <v>457000</v>
+      </c>
+    </row>
+    <row r="259" spans="13:14">
+      <c r="M259">
+        <v>2000</v>
+      </c>
+      <c r="N259">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="260" spans="13:14">
+      <c r="M260">
+        <v>2200</v>
+      </c>
+      <c r="N260">
+        <v>400000</v>
+      </c>
+    </row>
+    <row r="261" spans="13:14">
+      <c r="M261">
+        <v>1600</v>
+      </c>
+      <c r="N261">
+        <v>551500</v>
+      </c>
+    </row>
+    <row r="262" spans="13:14">
+      <c r="M262">
+        <v>3018</v>
+      </c>
+      <c r="N262">
+        <v>570000</v>
+      </c>
+    </row>
+    <row r="263" spans="13:14">
+      <c r="M263">
+        <v>3700</v>
+      </c>
+      <c r="N263">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="264" spans="13:14">
+      <c r="M264">
+        <v>2940</v>
+      </c>
+      <c r="N264">
+        <v>665000</v>
+      </c>
+    </row>
+    <row r="265" spans="13:14">
+      <c r="M265">
+        <v>1480</v>
+      </c>
+      <c r="N265">
+        <v>1325000</v>
+      </c>
+    </row>
+    <row r="266" spans="13:14">
+      <c r="M266">
+        <v>1360</v>
+      </c>
+      <c r="N266">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="267" spans="13:14">
+      <c r="M267">
+        <v>994</v>
+      </c>
+      <c r="N267">
+        <v>294000</v>
+      </c>
+    </row>
+    <row r="268" spans="13:14">
+      <c r="M268">
+        <v>2348</v>
+      </c>
+      <c r="N268">
+        <v>950000</v>
+      </c>
+    </row>
+    <row r="269" spans="13:14">
+      <c r="M269">
+        <v>1234</v>
+      </c>
+      <c r="N269">
+        <v>390000</v>
+      </c>
+    </row>
+    <row r="270" spans="13:14">
+      <c r="M270">
+        <v>3000</v>
+      </c>
+      <c r="N270">
+        <v>3050000</v>
+      </c>
+    </row>
+    <row r="271" spans="13:14">
+      <c r="M271">
+        <v>1496</v>
+      </c>
+      <c r="N271">
+        <v>730000</v>
+      </c>
+    </row>
+    <row r="272" spans="13:14">
+      <c r="M272">
+        <v>2454</v>
+      </c>
+      <c r="N272">
+        <v>230500</v>
+      </c>
+    </row>
+    <row r="273" spans="13:14">
+      <c r="M273">
+        <v>3453</v>
+      </c>
+      <c r="N273">
+        <v>1750000</v>
+      </c>
+    </row>
+    <row r="274" spans="13:14">
+      <c r="M274">
+        <v>2208</v>
+      </c>
+      <c r="N274">
+        <v>375000</v>
+      </c>
+    </row>
+    <row r="275" spans="13:14">
+      <c r="M275">
+        <v>1596</v>
+      </c>
+      <c r="N275">
+        <v>404586</v>
+      </c>
+    </row>
+    <row r="276" spans="13:14">
+      <c r="M276">
+        <v>1200</v>
+      </c>
+      <c r="N276">
+        <v>868000</v>
+      </c>
+    </row>
+    <row r="277" spans="13:14">
+      <c r="M277">
+        <v>1968</v>
+      </c>
+      <c r="N277">
+        <v>485000</v>
+      </c>
+    </row>
+    <row r="278" spans="13:14">
+      <c r="M278">
+        <v>1536</v>
+      </c>
+      <c r="N278">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="279" spans="13:14">
+      <c r="M279">
+        <v>2000</v>
+      </c>
+      <c r="N279">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="280" spans="13:14">
+      <c r="M280">
+        <v>2250</v>
+      </c>
+      <c r="N280">
+        <v>160000</v>
+      </c>
+    </row>
+    <row r="281" spans="13:14">
+      <c r="M281">
+        <v>3480</v>
+      </c>
+      <c r="N281">
+        <v>1150000</v>
+      </c>
+    </row>
+    <row r="282" spans="13:14">
+      <c r="M282">
+        <v>3450</v>
+      </c>
+      <c r="N282">
+        <v>1300000</v>
+      </c>
+    </row>
+    <row r="283" spans="13:14">
+      <c r="M283">
+        <v>2044</v>
+      </c>
+      <c r="N283">
+        <v>345000</v>
+      </c>
+    </row>
+    <row r="284" spans="13:14">
+      <c r="M284">
+        <v>1716</v>
+      </c>
+      <c r="N284">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="285" spans="13:14">
+      <c r="M285">
+        <v>1608</v>
+      </c>
+      <c r="N285">
+        <v>840520</v>
+      </c>
+    </row>
+    <row r="286" spans="13:14">
+      <c r="M286">
+        <v>5280</v>
+      </c>
+      <c r="N286">
+        <v>238780</v>
+      </c>
+    </row>
+    <row r="287" spans="13:14">
+      <c r="M287">
+        <v>1120</v>
+      </c>
+      <c r="N287">
+        <v>498200</v>
+      </c>
+    </row>
+    <row r="288" spans="13:14">
+      <c r="M288">
+        <v>2326</v>
+      </c>
+      <c r="N288">
+        <v>645000</v>
+      </c>
+    </row>
+    <row r="289" spans="13:14">
+      <c r="M289">
+        <v>1556</v>
+      </c>
+      <c r="N289">
+        <v>638000</v>
+      </c>
+    </row>
+    <row r="290" spans="13:14">
+      <c r="M290">
+        <v>879</v>
+      </c>
+      <c r="N290">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="291" spans="13:14">
+      <c r="M291">
+        <v>1640</v>
+      </c>
+      <c r="N291">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="292" spans="13:14">
+      <c r="M292">
+        <v>1920</v>
+      </c>
+      <c r="N292">
+        <v>630000</v>
+      </c>
+    </row>
+    <row r="293" spans="13:14">
+      <c r="M293">
+        <v>1354</v>
+      </c>
+      <c r="N293">
+        <v>337500</v>
+      </c>
+    </row>
+    <row r="294" spans="13:14">
+      <c r="M294">
+        <v>1234</v>
+      </c>
+      <c r="N294">
+        <v>345560</v>
+      </c>
+    </row>
+    <row r="295" spans="13:14">
+      <c r="M295">
+        <v>2400</v>
+      </c>
+      <c r="N295">
+        <v>610000</v>
+      </c>
+    </row>
+    <row r="296" spans="13:14">
+      <c r="M296">
+        <v>1914</v>
+      </c>
+      <c r="N296">
+        <v>535000</v>
+      </c>
+    </row>
+    <row r="297" spans="13:14">
+      <c r="M297">
+        <v>1510</v>
+      </c>
+      <c r="N297">
+        <v>740000</v>
+      </c>
+    </row>
+    <row r="298" spans="13:14">
+      <c r="M298">
+        <v>1120</v>
+      </c>
+      <c r="N298">
+        <v>451230</v>
+      </c>
+    </row>
+    <row r="299" spans="13:14">
+      <c r="M299">
+        <v>2800</v>
+      </c>
+      <c r="N299">
+        <v>643500</v>
+      </c>
+    </row>
+    <row r="300" spans="13:14">
+      <c r="M300">
+        <v>1305</v>
+      </c>
+      <c r="N300">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="301" spans="13:14">
+      <c r="M301">
+        <v>2943</v>
+      </c>
+      <c r="N301">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="302" spans="13:14">
+      <c r="M302">
+        <v>1332</v>
+      </c>
+      <c r="N302">
+        <v>55394</v>
+      </c>
+    </row>
+    <row r="303" spans="13:14">
+      <c r="M303">
+        <v>3219</v>
+      </c>
+      <c r="N303">
+        <v>715000</v>
+      </c>
+    </row>
+    <row r="304" spans="13:14">
+      <c r="M304">
+        <v>2360</v>
+      </c>
+      <c r="N304">
+        <v>640000</v>
+      </c>
+    </row>
+    <row r="305" spans="13:14">
+      <c r="M305">
+        <v>1134</v>
+      </c>
+      <c r="N305">
+        <v>435000</v>
+      </c>
+    </row>
+    <row r="306" spans="13:14">
+      <c r="M306">
+        <v>2860</v>
+      </c>
+      <c r="N306">
+        <v>530000</v>
+      </c>
+    </row>
+    <row r="307" spans="13:14">
+      <c r="M307">
+        <v>2220</v>
+      </c>
+      <c r="N307">
+        <v>1650000</v>
+      </c>
+    </row>
+    <row r="308" spans="13:14">
+      <c r="M308">
+        <v>4510</v>
+      </c>
+      <c r="N308">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="309" spans="13:14">
+      <c r="M309">
+        <v>1729</v>
+      </c>
+      <c r="N309">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="310" spans="13:14">
+      <c r="M310">
+        <v>1440</v>
+      </c>
+      <c r="N310">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="311" spans="13:14">
+      <c r="M311">
+        <v>2126</v>
+      </c>
+      <c r="N311">
+        <v>860000</v>
+      </c>
+    </row>
+    <row r="312" spans="13:14">
+      <c r="M312">
+        <v>2100</v>
+      </c>
+      <c r="N312">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="313" spans="13:14">
+      <c r="M313">
+        <v>1242</v>
+      </c>
+      <c r="N313">
+        <v>468000</v>
+      </c>
+    </row>
+    <row r="314" spans="13:14">
+      <c r="M314">
+        <v>1700</v>
+      </c>
+      <c r="N314">
+        <v>530000</v>
+      </c>
+    </row>
+    <row r="315" spans="13:14">
+      <c r="M315">
+        <v>1312</v>
+      </c>
+      <c r="N315">
+        <v>673000</v>
+      </c>
+    </row>
+    <row r="316" spans="13:14">
+      <c r="M316">
+        <v>2244</v>
+      </c>
+      <c r="N316">
+        <v>740000</v>
+      </c>
+    </row>
+    <row r="317" spans="13:14">
+      <c r="M317">
+        <v>2286</v>
+      </c>
+      <c r="N317">
+        <v>753403</v>
+      </c>
+    </row>
+    <row r="318" spans="13:14">
+      <c r="M318">
+        <v>1248</v>
+      </c>
+      <c r="N318">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="319" spans="13:14">
+      <c r="M319">
+        <v>2048</v>
+      </c>
+      <c r="N319">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="320" spans="13:14">
+      <c r="M320">
+        <v>3012</v>
+      </c>
+      <c r="N320">
+        <v>1320000</v>
+      </c>
+    </row>
+    <row r="321" spans="13:14">
+      <c r="M321">
+        <v>2370</v>
+      </c>
+      <c r="N321">
+        <v>1555677</v>
+      </c>
+    </row>
+    <row r="322" spans="13:14">
+      <c r="M322">
+        <v>2600</v>
+      </c>
+      <c r="N322">
+        <v>499000</v>
+      </c>
+    </row>
+    <row r="323" spans="13:14">
+      <c r="M323">
+        <v>3926</v>
+      </c>
+      <c r="N323">
+        <v>1450000</v>
+      </c>
+    </row>
+    <row r="324" spans="13:14">
+      <c r="M324">
+        <v>1670</v>
+      </c>
+      <c r="N324">
+        <v>840000</v>
+      </c>
+    </row>
+    <row r="325" spans="13:14">
+      <c r="M325">
+        <v>1584</v>
+      </c>
+      <c r="N325">
+        <v>655000</v>
+      </c>
+    </row>
+    <row r="326" spans="13:14">
+      <c r="M326">
+        <v>1620</v>
+      </c>
+      <c r="N326">
+        <v>783484</v>
+      </c>
+    </row>
+    <row r="327" spans="13:14">
+      <c r="M327">
+        <v>1176</v>
+      </c>
+      <c r="N327">
+        <v>480000</v>
+      </c>
+    </row>
+    <row r="328" spans="13:14">
+      <c r="M328">
+        <v>3082</v>
+      </c>
+      <c r="N328">
+        <v>1950000</v>
+      </c>
+    </row>
+    <row r="329" spans="13:14">
+      <c r="M329">
+        <v>2997</v>
+      </c>
+      <c r="N329">
+        <v>1120000</v>
+      </c>
+    </row>
+    <row r="330" spans="13:14">
+      <c r="M330">
+        <v>1450</v>
+      </c>
+      <c r="N330">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="331" spans="13:14">
+      <c r="M331">
+        <v>448</v>
+      </c>
+      <c r="N331">
+        <v>285500</v>
+      </c>
+    </row>
+    <row r="332" spans="13:14">
+      <c r="M332">
+        <v>1040</v>
+      </c>
+      <c r="N332">
+        <v>675000</v>
+      </c>
+    </row>
+    <row r="333" spans="13:14">
+      <c r="M333">
+        <v>1800</v>
+      </c>
+      <c r="N333">
+        <v>200000</v>
+      </c>
+    </row>
+    <row r="334" spans="13:14">
+      <c r="M334">
+        <v>3521</v>
+      </c>
+      <c r="N334">
+        <v>1110000</v>
+      </c>
+    </row>
+    <row r="335" spans="13:14">
+      <c r="M335">
+        <v>2424</v>
+      </c>
+      <c r="N335">
+        <v>1020000</v>
+      </c>
+    </row>
+    <row r="336" spans="13:14">
+      <c r="M336">
+        <v>3400</v>
+      </c>
+      <c r="N336">
+        <v>5510000</v>
+      </c>
+    </row>
+    <row r="337" spans="13:14">
+      <c r="M337">
+        <v>1824</v>
+      </c>
+      <c r="N337">
+        <v>3045000</v>
+      </c>
+    </row>
+    <row r="338" spans="13:14">
+      <c r="M338">
+        <v>1080</v>
+      </c>
+      <c r="N338">
+        <v>698000</v>
+      </c>
+    </row>
+    <row r="339" spans="13:14">
+      <c r="M339">
+        <v>2040</v>
+      </c>
+      <c r="N339">
+        <v>1300000</v>
+      </c>
+    </row>
+    <row r="340" spans="13:14">
+      <c r="M340">
+        <v>1696</v>
+      </c>
+      <c r="N340">
+        <v>920000</v>
+      </c>
+    </row>
+    <row r="341" spans="13:14">
+      <c r="M341">
+        <v>3496</v>
+      </c>
+      <c r="N341">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="342" spans="13:14">
+      <c r="M342">
+        <v>1624</v>
+      </c>
+      <c r="N342">
+        <v>290000</v>
+      </c>
+    </row>
+    <row r="343" spans="13:14">
+      <c r="M343">
+        <v>1653</v>
+      </c>
+      <c r="N343">
+        <v>992000</v>
+      </c>
+    </row>
+    <row r="344" spans="13:14">
+      <c r="M344">
+        <v>938</v>
+      </c>
+      <c r="N344">
+        <v>620000</v>
+      </c>
+    </row>
+    <row r="345" spans="13:14">
+      <c r="M345">
+        <v>2523</v>
+      </c>
+      <c r="N345">
+        <v>1648000</v>
+      </c>
+    </row>
+    <row r="346" spans="13:14">
+      <c r="M346">
+        <v>3900</v>
+      </c>
+      <c r="N346">
+        <v>2000000</v>
+      </c>
+    </row>
+    <row r="347" spans="13:14">
+      <c r="M347">
+        <v>3251</v>
+      </c>
+      <c r="N347">
+        <v>533000</v>
+      </c>
+    </row>
+    <row r="348" spans="13:14">
+      <c r="M348">
+        <v>850</v>
+      </c>
+      <c r="N348">
+        <v>499999</v>
+      </c>
+    </row>
+    <row r="349" spans="13:14">
+      <c r="M349">
+        <v>2160</v>
+      </c>
+      <c r="N349">
+        <v>835000</v>
+      </c>
+    </row>
+    <row r="350" spans="13:14">
+      <c r="M350">
+        <v>2246</v>
+      </c>
+      <c r="N350">
+        <v>715000</v>
+      </c>
+    </row>
+    <row r="351" spans="13:14">
+      <c r="M351">
+        <v>2281</v>
+      </c>
+      <c r="N351">
+        <v>470000</v>
+      </c>
+    </row>
+    <row r="352" spans="13:14">
+      <c r="M352">
+        <v>1280</v>
+      </c>
+      <c r="N352">
+        <v>396500</v>
+      </c>
+    </row>
+    <row r="353" spans="13:14">
+      <c r="M353">
+        <v>1744</v>
+      </c>
+      <c r="N353">
+        <v>729000</v>
+      </c>
+    </row>
+    <row r="354" spans="13:14">
+      <c r="M354">
+        <v>3720</v>
+      </c>
+      <c r="N354">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="355" spans="13:14">
+      <c r="M355">
+        <v>1732</v>
+      </c>
+      <c r="N355">
+        <v>728000</v>
+      </c>
+    </row>
+    <row r="356" spans="13:14">
+      <c r="M356">
+        <v>1120</v>
+      </c>
+      <c r="N356">
+        <v>352000</v>
+      </c>
+    </row>
+    <row r="357" spans="13:14">
+      <c r="M357">
+        <v>4860</v>
+      </c>
+      <c r="N357">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="358" spans="13:14">
+      <c r="M358">
+        <v>1080</v>
+      </c>
+      <c r="N358">
+        <v>690000</v>
+      </c>
+    </row>
+    <row r="359" spans="13:14">
+      <c r="M359">
+        <v>1125</v>
+      </c>
+      <c r="N359">
+        <v>625000</v>
+      </c>
+    </row>
+    <row r="360" spans="13:14">
+      <c r="M360">
+        <v>1368</v>
+      </c>
+      <c r="N360">
+        <v>325000</v>
+      </c>
+    </row>
+    <row r="361" spans="13:14">
+      <c r="M361">
+        <v>2680</v>
+      </c>
+      <c r="N361">
+        <v>630000</v>
+      </c>
+    </row>
+    <row r="362" spans="13:14">
+      <c r="M362">
+        <v>1224</v>
+      </c>
+      <c r="N362">
+        <v>740000</v>
+      </c>
+    </row>
+    <row r="363" spans="13:14">
+      <c r="M363">
+        <v>1868</v>
+      </c>
+      <c r="N363">
+        <v>385000</v>
+      </c>
+    </row>
+    <row r="364" spans="13:14">
+      <c r="M364">
+        <v>1728</v>
+      </c>
+      <c r="N364">
+        <v>380000</v>
+      </c>
+    </row>
+    <row r="365" spans="13:14">
+      <c r="M365">
+        <v>870</v>
+      </c>
+      <c r="N365">
+        <v>784000</v>
+      </c>
+    </row>
+    <row r="366" spans="13:14">
+      <c r="M366">
+        <v>2340</v>
+      </c>
+      <c r="N366">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="367" spans="13:14">
+      <c r="M367">
+        <v>1710</v>
+      </c>
+      <c r="N367">
+        <v>1275000</v>
+      </c>
+    </row>
+    <row r="368" spans="13:14">
+      <c r="M368">
+        <v>1280</v>
+      </c>
+      <c r="N368">
+        <v>469000</v>
+      </c>
+    </row>
+    <row r="369" spans="13:14">
+      <c r="M369">
+        <v>1980</v>
+      </c>
+      <c r="N369">
+        <v>1300000</v>
+      </c>
+    </row>
+    <row r="370" spans="13:14">
+      <c r="M370">
+        <v>3321</v>
+      </c>
+      <c r="N370">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="371" spans="13:14">
+      <c r="M371">
+        <v>2268</v>
+      </c>
+      <c r="N371">
+        <v>690000</v>
+      </c>
+    </row>
+    <row r="372" spans="13:14">
+      <c r="M372">
+        <v>1044</v>
+      </c>
+      <c r="N372">
+        <v>330000</v>
+      </c>
+    </row>
+    <row r="373" spans="13:14">
+      <c r="M373">
+        <v>1152</v>
+      </c>
+      <c r="N373">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="374" spans="13:14">
+      <c r="M374">
+        <v>1040</v>
+      </c>
+      <c r="N374">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="375" spans="13:14">
+      <c r="M375">
+        <v>1246</v>
+      </c>
+      <c r="N375">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="376" spans="13:14">
+      <c r="M376">
+        <v>625</v>
+      </c>
+      <c r="N376">
+        <v>245000</v>
+      </c>
+    </row>
+    <row r="377" spans="13:14">
+      <c r="M377">
+        <v>2400</v>
+      </c>
+      <c r="N377">
+        <v>541000</v>
+      </c>
+    </row>
+    <row r="378" spans="13:14">
+      <c r="M378">
+        <v>1440</v>
+      </c>
+      <c r="N378">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="379" spans="13:14">
+      <c r="M379">
+        <v>1024</v>
+      </c>
+      <c r="N379">
+        <v>106000</v>
+      </c>
+    </row>
+    <row r="380" spans="13:14">
+      <c r="M380">
+        <v>2490</v>
+      </c>
+      <c r="N380">
+        <v>680000</v>
+      </c>
+    </row>
+    <row r="381" spans="13:14">
+      <c r="M381">
+        <v>1658</v>
+      </c>
+      <c r="N381">
+        <v>390000</v>
+      </c>
+    </row>
+    <row r="382" spans="13:14">
+      <c r="M382">
+        <v>2940</v>
+      </c>
+      <c r="N382">
+        <v>2125000</v>
+      </c>
+    </row>
+    <row r="383" spans="13:14">
+      <c r="M383">
+        <v>1848</v>
+      </c>
+      <c r="N383">
+        <v>11750</v>
+      </c>
+    </row>
+    <row r="384" spans="13:14">
+      <c r="M384">
+        <v>1652</v>
+      </c>
+      <c r="N384">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="385" spans="13:14">
+      <c r="M385">
+        <v>2340</v>
+      </c>
+      <c r="N385">
+        <v>535000</v>
+      </c>
+    </row>
+    <row r="386" spans="13:14">
+      <c r="M386">
+        <v>3890</v>
+      </c>
+      <c r="N386">
+        <v>2700000</v>
+      </c>
+    </row>
+    <row r="387" spans="13:14">
+      <c r="M387">
+        <v>1564</v>
+      </c>
+      <c r="N387">
+        <v>333500</v>
+      </c>
+    </row>
+    <row r="388" spans="13:14">
+      <c r="M388">
+        <v>1428</v>
+      </c>
+      <c r="N388">
+        <v>565000</v>
+      </c>
+    </row>
+    <row r="389" spans="13:14">
+      <c r="M389">
+        <v>1152</v>
+      </c>
+      <c r="N389">
+        <v>370000</v>
+      </c>
+    </row>
+    <row r="390" spans="13:14">
+      <c r="M390">
+        <v>1920</v>
+      </c>
+      <c r="N390">
+        <v>870000</v>
+      </c>
+    </row>
+    <row r="391" spans="13:14">
+      <c r="M391">
+        <v>3975</v>
+      </c>
+      <c r="N391">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="392" spans="13:14">
+      <c r="M392">
+        <v>928</v>
+      </c>
+      <c r="N392">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="393" spans="13:14">
+      <c r="M393">
+        <v>3000</v>
+      </c>
+      <c r="N393">
+        <v>1210000</v>
+      </c>
+    </row>
+    <row r="394" spans="13:14">
+      <c r="M394">
+        <v>1800</v>
+      </c>
+      <c r="N394">
+        <v>860000</v>
+      </c>
+    </row>
+    <row r="395" spans="13:14">
+      <c r="M395">
+        <v>1288</v>
+      </c>
+      <c r="N395">
+        <v>460000</v>
+      </c>
+    </row>
+    <row r="396" spans="13:14">
+      <c r="M396">
+        <v>1820</v>
+      </c>
+      <c r="N396">
+        <v>659000</v>
+      </c>
+    </row>
+    <row r="397" spans="13:14">
+      <c r="M397">
+        <v>1984</v>
+      </c>
+      <c r="N397">
+        <v>494000</v>
+      </c>
+    </row>
+    <row r="398" spans="13:14">
+      <c r="M398">
+        <v>1144</v>
+      </c>
+      <c r="N398">
+        <v>350000</v>
+      </c>
+    </row>
+    <row r="399" spans="13:14">
+      <c r="M399">
+        <v>3090</v>
+      </c>
+      <c r="N399">
+        <v>1600000</v>
+      </c>
+    </row>
+    <row r="400" spans="13:14">
+      <c r="M400">
+        <v>2130</v>
+      </c>
+      <c r="N400">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="401" spans="13:14">
+      <c r="M401">
+        <v>1492</v>
+      </c>
+      <c r="N401">
+        <v>393000</v>
+      </c>
+    </row>
+    <row r="402" spans="13:14">
+      <c r="M402">
+        <v>1588</v>
+      </c>
+      <c r="N402">
+        <v>660000</v>
+      </c>
+    </row>
+    <row r="403" spans="13:14">
+      <c r="M403">
+        <v>1616</v>
+      </c>
+      <c r="N403">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="404" spans="13:14">
+      <c r="M404">
+        <v>6630</v>
+      </c>
+      <c r="N404">
+        <v>5200000</v>
+      </c>
+    </row>
+    <row r="405" spans="13:14">
+      <c r="M405">
+        <v>3069</v>
+      </c>
+      <c r="N405">
+        <v>1330000</v>
+      </c>
+    </row>
+    <row r="406" spans="13:14">
+      <c r="M406">
+        <v>1695</v>
+      </c>
+      <c r="N406">
+        <v>970000</v>
+      </c>
+    </row>
+    <row r="407" spans="13:14">
+      <c r="M407">
+        <v>2440</v>
+      </c>
+      <c r="N407">
+        <v>935000</v>
+      </c>
+    </row>
+    <row r="408" spans="13:14">
+      <c r="M408">
+        <v>3087</v>
+      </c>
+      <c r="N408">
+        <v>466440</v>
+      </c>
+    </row>
+    <row r="409" spans="13:14">
+      <c r="M409">
+        <v>1848</v>
+      </c>
+      <c r="N409">
+        <v>425000</v>
+      </c>
+    </row>
+    <row r="410" spans="13:14">
+      <c r="M410">
+        <v>2000</v>
+      </c>
+      <c r="N410">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="411" spans="13:14">
+      <c r="M411">
+        <v>1776</v>
+      </c>
+      <c r="N411">
+        <v>660000</v>
+      </c>
+    </row>
+    <row r="412" spans="13:14">
+      <c r="M412">
+        <v>1240</v>
+      </c>
+      <c r="N412">
+        <v>390000</v>
+      </c>
+    </row>
+    <row r="413" spans="13:14">
+      <c r="M413">
+        <v>1900</v>
+      </c>
+      <c r="N413">
+        <v>748000</v>
+      </c>
+    </row>
+    <row r="414" spans="13:14">
+      <c r="M414">
+        <v>1278</v>
+      </c>
+      <c r="N414">
+        <v>505000</v>
+      </c>
+    </row>
+    <row r="415" spans="13:14">
+      <c r="M415">
+        <v>3288</v>
+      </c>
+      <c r="N415">
+        <v>882500</v>
+      </c>
+    </row>
+    <row r="416" spans="13:14">
+      <c r="M416">
+        <v>1778</v>
+      </c>
+      <c r="N416">
+        <v>328730</v>
+      </c>
+    </row>
+    <row r="417" spans="13:14">
+      <c r="M417">
+        <v>3768</v>
+      </c>
+      <c r="N417">
+        <v>2232500</v>
+      </c>
+    </row>
+    <row r="418" spans="13:14">
+      <c r="M418">
+        <v>1120</v>
+      </c>
+      <c r="N418">
+        <v>670000</v>
+      </c>
+    </row>
+    <row r="419" spans="13:14">
+      <c r="M419">
+        <v>5625</v>
+      </c>
+      <c r="N419">
+        <v>197500</v>
+      </c>
+    </row>
+    <row r="420" spans="13:14">
+      <c r="M420">
+        <v>3060</v>
+      </c>
+      <c r="N420">
+        <v>561000</v>
+      </c>
+    </row>
+    <row r="421" spans="13:14">
+      <c r="M421">
+        <v>1950</v>
+      </c>
+      <c r="N421">
+        <v>659000</v>
+      </c>
+    </row>
+    <row r="422" spans="13:14">
+      <c r="M422">
+        <v>1683</v>
+      </c>
+      <c r="N422">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="423" spans="13:14">
+      <c r="M423">
+        <v>1680</v>
+      </c>
+      <c r="N423">
+        <v>830000</v>
+      </c>
+    </row>
+    <row r="424" spans="13:14">
+      <c r="M424">
+        <v>1169</v>
+      </c>
+      <c r="N424">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="425" spans="13:14">
+      <c r="M425">
+        <v>2213</v>
+      </c>
+      <c r="N425">
+        <v>975000</v>
+      </c>
+    </row>
+    <row r="426" spans="13:14">
+      <c r="M426">
+        <v>2880</v>
+      </c>
+      <c r="N426">
+        <v>2950000</v>
+      </c>
+    </row>
+    <row r="427" spans="13:14">
+      <c r="M427">
+        <v>2800</v>
+      </c>
+      <c r="N427">
+        <v>1180000</v>
+      </c>
+    </row>
+    <row r="428" spans="13:14">
+      <c r="M428">
+        <v>2394</v>
+      </c>
+      <c r="N428">
+        <v>530000</v>
+      </c>
+    </row>
+    <row r="429" spans="13:14">
+      <c r="M429">
+        <v>1980</v>
+      </c>
+      <c r="N429">
+        <v>1175000</v>
+      </c>
+    </row>
+    <row r="430" spans="13:14">
+      <c r="M430">
+        <v>2400</v>
+      </c>
+      <c r="N430">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="431" spans="13:14">
+      <c r="M431">
+        <v>968</v>
+      </c>
+      <c r="N431">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="432" spans="13:14">
+      <c r="M432">
+        <v>3180</v>
+      </c>
+      <c r="N432">
+        <v>984000</v>
+      </c>
+    </row>
+    <row r="433" spans="13:14">
+      <c r="M433">
+        <v>1328</v>
+      </c>
+      <c r="N433">
+        <v>300000</v>
+      </c>
+    </row>
+    <row r="434" spans="13:14">
+      <c r="M434">
+        <v>1880</v>
+      </c>
+      <c r="N434">
+        <v>995000</v>
+      </c>
+    </row>
+    <row r="435" spans="13:14">
+      <c r="M435">
+        <v>3270</v>
+      </c>
+      <c r="N435">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="436" spans="13:14">
+      <c r="M436">
+        <v>1364</v>
+      </c>
+      <c r="N436">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="437" spans="13:14">
+      <c r="M437">
+        <v>1938</v>
+      </c>
+      <c r="N437">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="438" spans="13:14">
+      <c r="M438">
+        <v>3968</v>
+      </c>
+      <c r="N438">
+        <v>591700</v>
+      </c>
+    </row>
+    <row r="439" spans="13:14">
+      <c r="M439">
+        <v>1880</v>
+      </c>
+      <c r="N439">
+        <v>418000</v>
+      </c>
+    </row>
+    <row r="440" spans="13:14">
+      <c r="M440">
+        <v>1362</v>
+      </c>
+      <c r="N440">
+        <v>700000</v>
+      </c>
+    </row>
+    <row r="441" spans="13:14">
+      <c r="M441">
+        <v>2500</v>
+      </c>
+      <c r="N441">
+        <v>685000</v>
+      </c>
+    </row>
+    <row r="442" spans="13:14">
+      <c r="M442">
+        <v>2704</v>
+      </c>
+      <c r="N442">
+        <v>410000</v>
+      </c>
+    </row>
+    <row r="443" spans="13:14">
+      <c r="M443">
+        <v>1534</v>
+      </c>
+      <c r="N443">
+        <v>655000</v>
+      </c>
+    </row>
+    <row r="444" spans="13:14">
+      <c r="M444">
+        <v>808</v>
+      </c>
+      <c r="N444">
+        <v>335000</v>
+      </c>
+    </row>
+    <row r="445" spans="13:14">
+      <c r="M445">
+        <v>1548</v>
+      </c>
+      <c r="N445">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="446" spans="13:14">
+      <c r="M446">
+        <v>1626</v>
+      </c>
+      <c r="N446">
+        <v>860000</v>
+      </c>
+    </row>
+    <row r="447" spans="13:14">
+      <c r="M447">
+        <v>2242</v>
+      </c>
+      <c r="N447">
+        <v>630000</v>
+      </c>
+    </row>
+    <row r="448" spans="13:14">
+      <c r="M448">
+        <v>2178</v>
+      </c>
+      <c r="N448">
+        <v>1200000</v>
+      </c>
+    </row>
+    <row r="449" spans="13:14">
+      <c r="M449">
+        <v>1737</v>
+      </c>
+      <c r="N449">
+        <v>455000</v>
+      </c>
+    </row>
+    <row r="450" spans="13:14">
+      <c r="M450">
+        <v>938</v>
+      </c>
+      <c r="N450">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="451" spans="13:14">
+      <c r="M451">
+        <v>3320</v>
+      </c>
+      <c r="N451">
+        <v>260000</v>
+      </c>
+    </row>
+    <row r="452" spans="13:14">
+      <c r="M452">
+        <v>1010</v>
+      </c>
+      <c r="N452">
+        <v>319000</v>
+      </c>
+    </row>
+    <row r="453" spans="13:14">
+      <c r="M453">
+        <v>2220</v>
+      </c>
+      <c r="N453">
+        <v>505000</v>
+      </c>
+    </row>
+    <row r="454" spans="13:14">
+      <c r="M454">
+        <v>2500</v>
+      </c>
+      <c r="N454">
+        <v>1250000</v>
+      </c>
+    </row>
+    <row r="455" spans="13:14">
+      <c r="M455">
+        <v>2236</v>
+      </c>
+      <c r="N455">
+        <v>1048000</v>
+      </c>
+    </row>
+    <row r="456" spans="13:14">
+      <c r="M456">
+        <v>6000</v>
+      </c>
+      <c r="N456">
+        <v>2720000</v>
+      </c>
+    </row>
+    <row r="457" spans="13:14">
+      <c r="M457">
+        <v>1080</v>
+      </c>
+      <c r="N457">
+        <v>628000</v>
+      </c>
+    </row>
+    <row r="458" spans="13:14">
+      <c r="M458">
+        <v>1668</v>
+      </c>
+      <c r="N458">
+        <v>475000</v>
+      </c>
+    </row>
+    <row r="459" spans="13:14">
+      <c r="M459">
+        <v>928</v>
+      </c>
+      <c r="N459">
+        <v>295000</v>
+      </c>
+    </row>
+    <row r="460" spans="13:14">
+      <c r="M460">
+        <v>2560</v>
+      </c>
+      <c r="N460">
+        <v>825000</v>
+      </c>
+    </row>
+    <row r="461" spans="13:14">
+      <c r="M461">
+        <v>1304</v>
+      </c>
+      <c r="N461">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="462" spans="13:14">
+      <c r="M462">
+        <v>1064</v>
+      </c>
+      <c r="N462">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="463" spans="13:14">
+      <c r="M463">
+        <v>1080</v>
+      </c>
+      <c r="N463">
+        <v>385000</v>
+      </c>
+    </row>
+    <row r="464" spans="13:14">
+      <c r="M464">
+        <v>1620</v>
+      </c>
+      <c r="N464">
+        <v>299250</v>
+      </c>
+    </row>
+    <row r="465" spans="13:14">
+      <c r="M465">
+        <v>1400</v>
+      </c>
+      <c r="N465">
+        <v>1550000</v>
+      </c>
+    </row>
+    <row r="466" spans="13:14">
+      <c r="M466">
+        <v>1592</v>
+      </c>
+      <c r="N466">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="467" spans="13:14">
+      <c r="M467">
+        <v>1598</v>
+      </c>
+      <c r="N467">
+        <v>475000</v>
+      </c>
+    </row>
+    <row r="468" spans="13:14">
+      <c r="M468">
+        <v>1488</v>
+      </c>
+      <c r="N468">
+        <v>382203</v>
+      </c>
+    </row>
+    <row r="469" spans="13:14">
+      <c r="M469">
+        <v>3301</v>
+      </c>
+      <c r="N469">
+        <v>735000</v>
+      </c>
+    </row>
+    <row r="470" spans="13:14">
+      <c r="M470">
+        <v>3265</v>
+      </c>
+      <c r="N470">
+        <v>1250000</v>
+      </c>
+    </row>
+    <row r="471" spans="13:14">
+      <c r="M471">
+        <v>2316</v>
+      </c>
+      <c r="N471">
+        <v>928500</v>
+      </c>
+    </row>
+    <row r="472" spans="13:14">
+      <c r="M472">
+        <v>1728</v>
+      </c>
+      <c r="N472">
+        <v>540000</v>
+      </c>
+    </row>
+    <row r="473" spans="13:14">
+      <c r="M473">
+        <v>1386</v>
+      </c>
+      <c r="N473">
+        <v>524000</v>
+      </c>
+    </row>
+    <row r="474" spans="13:14">
+      <c r="M474">
+        <v>2999</v>
+      </c>
+      <c r="N474">
+        <v>1230000</v>
+      </c>
+    </row>
+    <row r="475" spans="13:14">
+      <c r="M475">
+        <v>1771</v>
+      </c>
+      <c r="N475">
+        <v>650000</v>
+      </c>
+    </row>
+    <row r="476" spans="13:14">
+      <c r="M476">
+        <v>2280</v>
+      </c>
+      <c r="N476">
+        <v>1250000</v>
+      </c>
+    </row>
+    <row r="477" spans="13:14">
+      <c r="M477">
+        <v>1216</v>
+      </c>
+      <c r="N477">
+        <v>505000</v>
+      </c>
+    </row>
+    <row r="478" spans="13:14">
+      <c r="M478">
+        <v>952</v>
+      </c>
+      <c r="N478">
+        <v>465000</v>
+      </c>
+    </row>
+    <row r="479" spans="13:14">
+      <c r="M479">
+        <v>1870</v>
+      </c>
+      <c r="N479">
+        <v>630000</v>
+      </c>
+    </row>
+    <row r="480" spans="13:14">
+      <c r="M480">
+        <v>1128</v>
+      </c>
+      <c r="N480">
+        <v>640000</v>
+      </c>
+    </row>
+    <row r="481" spans="13:14">
+      <c r="M481">
+        <v>992</v>
+      </c>
+      <c r="N481">
+        <v>786000</v>
+      </c>
+    </row>
+    <row r="482" spans="13:14">
+      <c r="M482">
+        <v>1785</v>
+      </c>
+      <c r="N482">
+        <v>520000</v>
+      </c>
+    </row>
+    <row r="483" spans="13:14">
+      <c r="M483">
+        <v>1012</v>
+      </c>
+      <c r="N483">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="484" spans="13:14">
+      <c r="M484">
+        <v>2208</v>
+      </c>
+      <c r="N484">
+        <v>830000</v>
+      </c>
+    </row>
+    <row r="485" spans="13:14">
+      <c r="M485">
+        <v>1729</v>
+      </c>
+      <c r="N485">
+        <v>545000</v>
+      </c>
+    </row>
+    <row r="486" spans="13:14">
+      <c r="M486">
+        <v>2100</v>
+      </c>
+      <c r="N486">
+        <v>600000</v>
+      </c>
+    </row>
+    <row r="487" spans="13:14">
+      <c r="M487">
+        <v>2271</v>
+      </c>
+      <c r="N487">
+        <v>1100000</v>
+      </c>
+    </row>
+    <row r="488" spans="13:14">
+      <c r="M488">
+        <v>4408</v>
+      </c>
+      <c r="N488">
+        <v>1780000</v>
+      </c>
+    </row>
+    <row r="489" spans="13:14">
+      <c r="M489">
+        <v>1944</v>
+      </c>
+      <c r="N489">
+        <v>425000</v>
+      </c>
+    </row>
+    <row r="490" spans="13:14">
+      <c r="M490">
+        <v>2358</v>
+      </c>
+      <c r="N490">
+        <v>860000</v>
+      </c>
+    </row>
+    <row r="491" spans="13:14">
+      <c r="M491">
+        <v>1633</v>
+      </c>
+      <c r="N491">
+        <v>738000</v>
+      </c>
+    </row>
+    <row r="492" spans="13:14">
+      <c r="M492">
+        <v>1552</v>
+      </c>
+      <c r="N492">
+        <v>150000</v>
+      </c>
+    </row>
+    <row r="493" spans="13:14">
+      <c r="M493">
+        <v>1344</v>
+      </c>
+      <c r="N493">
+        <v>341250</v>
+      </c>
+    </row>
+    <row r="494" spans="13:14">
+      <c r="M494">
+        <v>1740</v>
+      </c>
+      <c r="N494">
+        <v>420000</v>
+      </c>
+    </row>
+    <row r="495" spans="13:14">
+      <c r="M495">
+        <v>2622</v>
+      </c>
+      <c r="N495">
+        <v>1400000</v>
+      </c>
+    </row>
+    <row r="496" spans="13:14">
+      <c r="M496">
+        <v>3860</v>
+      </c>
+      <c r="N496">
+        <v>2850000</v>
+      </c>
+    </row>
+    <row r="497" spans="13:14">
+      <c r="M497">
+        <v>1633</v>
+      </c>
+      <c r="N497">
+        <v>355000</v>
+      </c>
+    </row>
+    <row r="498" spans="13:14">
+      <c r="M498">
+        <v>3360</v>
+      </c>
+      <c r="N498">
+        <v>1651000</v>
+      </c>
+    </row>
+    <row r="499" spans="13:14">
+      <c r="M499">
+        <v>1980</v>
+      </c>
+      <c r="N499">
+        <v>280000</v>
+      </c>
+    </row>
+    <row r="500" spans="13:14">
+      <c r="M500">
+        <v>1872</v>
+      </c>
+      <c r="N500">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="501" spans="13:14">
+      <c r="M501">
+        <v>3078</v>
+      </c>
+      <c r="N501">
+        <v>974000</v>
       </c>
     </row>
   </sheetData>
@@ -2594,7 +9947,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V77"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="2.7109375" customWidth="1"/>
@@ -2605,7 +9958,7 @@
     <row r="1" spans="2:22" ht="6" customHeight="1"/>
     <row r="2" spans="2:22" ht="52" customHeight="1">
       <c r="B2" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C2" s="3"/>
       <c r="D2" s="3"/>
@@ -2630,7 +9983,7 @@
     </row>
     <row r="3" spans="2:22" ht="28" customHeight="1">
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C3" s="4"/>
       <c r="D3" s="4"/>
@@ -2656,7 +10009,7 @@
     <row r="4" spans="2:22" ht="8" customHeight="1"/>
     <row r="5" spans="2:22" ht="20" customHeight="1">
       <c r="B5" s="5" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C5" s="5"/>
       <c r="D5" s="5"/>
@@ -2668,7 +10021,7 @@
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
       <c r="M5" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N5" s="5"/>
       <c r="O5" s="5"/>
@@ -2684,27 +10037,27 @@
     <row r="7" spans="2:22" ht="20" customHeight="1"/>
     <row r="8" spans="2:22" ht="26" customHeight="1">
       <c r="B8" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="F8" s="7" t="s">
         <v>1</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="R8" s="7" t="s">
         <v>1</v>
       </c>
       <c r="S8" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="29" spans="2:22">
       <c r="B29" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C29" s="5"/>
       <c r="D29" s="5"/>
@@ -2716,7 +10069,7 @@
       <c r="J29" s="5"/>
       <c r="K29" s="5"/>
       <c r="M29" s="5" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N29" s="5"/>
       <c r="O29" s="5"/>
@@ -2732,59 +10085,267 @@
     <row r="31" spans="2:22" ht="20" customHeight="1"/>
     <row r="32" spans="2:22" ht="26" customHeight="1">
       <c r="E32" s="6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F32" s="7" t="s">
         <v>1</v>
       </c>
       <c r="G32" s="8" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="Q32" s="6" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="R32" s="7" t="s">
         <v>1</v>
       </c>
       <c r="S32" s="8" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="55" spans="2:9" ht="8" customHeight="1"/>
-    <row r="56" spans="2:9" ht="28" customHeight="1">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="55" spans="2:22" ht="8" customHeight="1"/>
+    <row r="56" spans="2:22" ht="28" customHeight="1">
       <c r="B56" s="9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C56" s="10">
         <v>58400</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E56" s="11">
         <v>640000</v>
       </c>
       <c r="F56" s="9" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G56" s="11">
         <v>89333900102</v>
       </c>
       <c r="H56" s="9" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="I56" s="12" t="s">
         <v>8</v>
       </c>
     </row>
+    <row r="58" spans="2:22" ht="8" customHeight="1"/>
+    <row r="59" spans="2:22" ht="40" customHeight="1">
+      <c r="B59" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="C59" s="13"/>
+      <c r="D59" s="13"/>
+      <c r="E59" s="13"/>
+      <c r="F59" s="13"/>
+      <c r="G59" s="13"/>
+      <c r="H59" s="13"/>
+      <c r="I59" s="13"/>
+      <c r="J59" s="13"/>
+      <c r="K59" s="13"/>
+      <c r="L59" s="13"/>
+      <c r="M59" s="13"/>
+      <c r="N59" s="13"/>
+      <c r="O59" s="13"/>
+      <c r="P59" s="13"/>
+      <c r="Q59" s="13"/>
+      <c r="R59" s="13"/>
+      <c r="S59" s="13"/>
+      <c r="T59" s="13"/>
+      <c r="U59" s="13"/>
+      <c r="V59" s="13"/>
+    </row>
+    <row r="60" spans="2:22" ht="22" customHeight="1">
+      <c r="B60" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C60" s="14"/>
+      <c r="D60" s="14"/>
+      <c r="E60" s="14"/>
+      <c r="F60" s="14"/>
+      <c r="G60" s="14"/>
+      <c r="H60" s="14"/>
+      <c r="I60" s="14"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+      <c r="M60" s="14"/>
+      <c r="N60" s="14"/>
+      <c r="O60" s="14"/>
+      <c r="P60" s="14"/>
+      <c r="Q60" s="14"/>
+      <c r="R60" s="14"/>
+      <c r="S60" s="14"/>
+      <c r="T60" s="14"/>
+      <c r="U60" s="14"/>
+      <c r="V60" s="14"/>
+    </row>
+    <row r="61" spans="2:22" ht="20" customHeight="1">
+      <c r="N61" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="O61" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="P61" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="62" spans="2:22" ht="20" customHeight="1"/>
+    <row r="63" spans="2:22">
+      <c r="N63" s="16" t="s">
+        <v>32</v>
+      </c>
+      <c r="O63" s="17">
+        <v>0.4900781274151763</v>
+      </c>
+      <c r="P63" s="18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="64" spans="2:22">
+      <c r="N64" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="O64" s="17">
+        <v>0.3156383679747683</v>
+      </c>
+      <c r="P64" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="65" spans="14:16">
+      <c r="N65" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="O65" s="17">
+        <v>0.2783911419840776</v>
+      </c>
+      <c r="P65" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="66" spans="14:16">
+      <c r="N66" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="O66" s="17">
+        <v>-0.1685112144467334</v>
+      </c>
+      <c r="P66" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="67" spans="14:16">
+      <c r="N67" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="O67" s="17">
+        <v>-0.02146980648093806</v>
+      </c>
+      <c r="P67" s="19" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="69" spans="14:16">
+      <c r="N69" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="O69" s="15"/>
+      <c r="P69" s="15"/>
+    </row>
+    <row r="70" spans="14:16">
+      <c r="N70" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="O70" s="21" t="s">
+        <v>33</v>
+      </c>
+      <c r="P70" s="21"/>
+    </row>
+    <row r="71" spans="14:16">
+      <c r="N71" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="O71" s="21" t="s">
+        <v>32</v>
+      </c>
+      <c r="P71" s="21"/>
+    </row>
+    <row r="72" spans="14:16">
+      <c r="N72" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="O72" s="22">
+        <v>0.4901</v>
+      </c>
+      <c r="P72" s="22"/>
+    </row>
+    <row r="73" spans="14:16">
+      <c r="N73" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="O73" s="22">
+        <v>0.2402</v>
+      </c>
+      <c r="P73" s="22"/>
+    </row>
+    <row r="74" spans="14:16">
+      <c r="N74" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="O74" s="22">
+        <v>380.07</v>
+      </c>
+      <c r="P74" s="22"/>
+    </row>
+    <row r="75" spans="14:16">
+      <c r="N75" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="O75" s="22">
+        <v>15674.87</v>
+      </c>
+      <c r="P75" s="22"/>
+    </row>
+    <row r="76" spans="14:16">
+      <c r="N76" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="O76" s="22">
+        <v>0</v>
+      </c>
+      <c r="P76" s="22"/>
+    </row>
+    <row r="77" spans="14:16">
+      <c r="N77" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="O77" s="21">
+        <v>500</v>
+      </c>
+      <c r="P77" s="21"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="17">
     <mergeCell ref="B2:V2"/>
     <mergeCell ref="B3:V3"/>
     <mergeCell ref="B5:K5"/>
     <mergeCell ref="M5:V5"/>
     <mergeCell ref="B29:K29"/>
     <mergeCell ref="M29:V29"/>
+    <mergeCell ref="B59:V59"/>
+    <mergeCell ref="B60:V60"/>
+    <mergeCell ref="N69:P69"/>
+    <mergeCell ref="O70:P70"/>
+    <mergeCell ref="O71:P71"/>
+    <mergeCell ref="O72:P72"/>
+    <mergeCell ref="O73:P73"/>
+    <mergeCell ref="O74:P74"/>
+    <mergeCell ref="O75:P75"/>
+    <mergeCell ref="O76:P76"/>
+    <mergeCell ref="O77:P77"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Q1 Filter" prompt="Select a building class (or All)" sqref="F8">
@@ -2807,38 +10368,38 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E22"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="2" width="22.7109375" customWidth="1"/>
     <col min="3" max="6" width="18.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:6">
       <c r="A1" s="1" t="s">
-        <v>45</v>
+        <v>67</v>
       </c>
       <c r="B1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>47</v>
+        <v>69</v>
       </c>
       <c r="E1" s="1"/>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>25</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -2852,7 +10413,7 @@
         <v>48196553515</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:6">
       <c r="A4" t="s">
         <v>9</v>
       </c>
@@ -2866,7 +10427,7 @@
         <v>4160093747</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2880,7 +10441,7 @@
         <v>20066297827</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:6">
       <c r="A6" t="s">
         <v>11</v>
       </c>
@@ -2894,7 +10455,7 @@
         <v>13644275513</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:6">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -2908,62 +10469,121 @@
         <v>3266679500</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:6">
       <c r="A9" s="1" t="s">
-        <v>49</v>
+        <v>71</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
-    </row>
-    <row r="10" spans="1:5">
+      <c r="D9" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+    </row>
+    <row r="10" spans="1:6">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="D10" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11">
         <v>5365</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="D11" t="s">
+        <v>32</v>
+      </c>
+      <c r="E11">
+        <v>0.4901</v>
+      </c>
+      <c r="F11">
+        <v>0.2402</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12">
         <v>4475</v>
       </c>
-    </row>
-    <row r="13" spans="1:5">
+      <c r="D12" t="s">
+        <v>53</v>
+      </c>
+      <c r="E12">
+        <v>0.3156</v>
+      </c>
+      <c r="F12">
+        <v>0.09959999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" t="s">
         <v>15</v>
       </c>
       <c r="B13">
         <v>4684</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
+      <c r="D13" t="s">
+        <v>54</v>
+      </c>
+      <c r="E13">
+        <v>0.2784</v>
+      </c>
+      <c r="F13">
+        <v>0.0775</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" t="s">
         <v>16</v>
       </c>
       <c r="B14">
         <v>5279</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
+      <c r="D14" t="s">
+        <v>56</v>
+      </c>
+      <c r="E14">
+        <v>-0.1685</v>
+      </c>
+      <c r="F14">
+        <v>0.0284</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
       <c r="A15" t="s">
         <v>17</v>
       </c>
       <c r="B15">
         <v>4711</v>
       </c>
-    </row>
-    <row r="16" spans="1:5">
+      <c r="D15" t="s">
+        <v>57</v>
+      </c>
+      <c r="E15">
+        <v>-0.0215</v>
+      </c>
+      <c r="F15">
+        <v>0.0005</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -3020,10 +10640,11 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="D1:E1"/>
     <mergeCell ref="A9:C9"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
